--- a/Semiconductor/QCOMM.xlsx
+++ b/Semiconductor/QCOMM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jameelbrannon/Library/CloudStorage/Dropbox/models/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{218BFB74-9696-284B-A0DB-8AECFB6DAFD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE042555-5B98-5942-8B6F-300EC625F59A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="13280" yWindow="2960" windowWidth="32260" windowHeight="24440" xr2:uid="{4BC02444-90DA-5044-8491-8B526222F964}"/>
   </bookViews>
@@ -179,7 +179,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="112">
   <si>
     <t>P</t>
   </si>
@@ -506,6 +506,15 @@
   </si>
   <si>
     <t>Akash Palkhiwala</t>
+  </si>
+  <si>
+    <t>DIO</t>
+  </si>
+  <si>
+    <t>DPO</t>
+  </si>
+  <si>
+    <t>DSO</t>
   </si>
 </sst>
 </file>
@@ -681,7 +690,7 @@
     <xdr:to>
       <xdr:col>15</xdr:col>
       <xdr:colOff>25400</xdr:colOff>
-      <xdr:row>88</xdr:row>
+      <xdr:row>94</xdr:row>
       <xdr:rowOff>44393</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -731,7 +740,7 @@
     <xdr:to>
       <xdr:col>31</xdr:col>
       <xdr:colOff>19181</xdr:colOff>
-      <xdr:row>88</xdr:row>
+      <xdr:row>94</xdr:row>
       <xdr:rowOff>38100</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -1297,7 +1306,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51D93CA2-0C16-D24F-BC55-74E1F5B20515}">
-  <dimension ref="B1:IG83"/>
+  <dimension ref="B1:IG89"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="1.5" style="1" customWidth="1"/>
@@ -2815,7 +2824,7 @@
         <v>1300</v>
       </c>
       <c r="AD8" s="16">
-        <f t="shared" ref="U8:AD8" si="38">+AD7</f>
+        <f t="shared" ref="AD8" si="38">+AD7</f>
         <v>5572</v>
       </c>
       <c r="AE8" s="16">
@@ -2975,7 +2984,7 @@
         <v>0</v>
       </c>
       <c r="AD10" s="16">
-        <f t="shared" ref="U10:AD10" si="57">+AD9</f>
+        <f t="shared" ref="AD10" si="57">+AD9</f>
         <v>18</v>
       </c>
       <c r="AE10" s="16">
@@ -3024,27 +3033,27 @@
         <v>10199</v>
       </c>
       <c r="K11" s="19">
-        <f>SUM(K6,K8,K10)</f>
+        <f t="shared" ref="K11:P11" si="59">SUM(K6,K8,K10)</f>
         <v>11619</v>
       </c>
       <c r="L11" s="19">
-        <f>SUM(L6,L8,L10)</f>
+        <f t="shared" si="59"/>
         <v>10788</v>
       </c>
       <c r="M11" s="19">
-        <f>SUM(M6,M8,M10)</f>
+        <f t="shared" si="59"/>
         <v>10311</v>
       </c>
       <c r="N11" s="19">
-        <f>SUM(N6,N8,N10)</f>
+        <f t="shared" si="59"/>
         <v>11231</v>
       </c>
       <c r="O11" s="19">
-        <f>SUM(O6,O8,O10)</f>
+        <f t="shared" si="59"/>
         <v>12205</v>
       </c>
       <c r="P11" s="19">
-        <f>SUM(P6,P8,P10)</f>
+        <f t="shared" si="59"/>
         <v>10390.77</v>
       </c>
       <c r="AD11" s="12">
@@ -3064,35 +3073,35 @@
         <v>49543.607600000003</v>
       </c>
       <c r="AH11" s="12">
-        <f t="shared" ref="AH11:AO11" si="59">SUM(AH6,AH8,AH10)</f>
+        <f t="shared" ref="AH11:AO11" si="60">SUM(AH6,AH8,AH10)</f>
         <v>53901.786867999996</v>
       </c>
       <c r="AI11" s="12">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>58440.927742440013</v>
       </c>
       <c r="AJ11" s="12">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>63004.939473085207</v>
       </c>
       <c r="AK11" s="12">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>67421.860812744533</v>
       </c>
       <c r="AL11" s="12">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>72180.462325567234</v>
       </c>
       <c r="AM11" s="12">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>77309.444764395885</v>
       </c>
       <c r="AN11" s="12">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>82840.068260819011</v>
       </c>
       <c r="AO11" s="12">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>88806.389741553445</v>
       </c>
     </row>
@@ -3204,7 +3213,7 @@
         <v>1343</v>
       </c>
       <c r="F15" s="10">
-        <f t="shared" ref="F15:F26" si="60">+AC15-SUM(C15:E15)</f>
+        <f t="shared" ref="F15:F26" si="61">+AC15-SUM(C15:E15)</f>
         <v>1341</v>
       </c>
       <c r="G15" s="10">
@@ -3217,7 +3226,7 @@
         <v>1400</v>
       </c>
       <c r="J15" s="10">
-        <f t="shared" ref="J15:J26" si="61">+AD15-SUM(G15:I15)</f>
+        <f t="shared" ref="J15:J26" si="62">+AD15-SUM(G15:I15)</f>
         <v>1713</v>
       </c>
       <c r="K15" s="10">
@@ -3230,7 +3239,7 @@
         <v>1472</v>
       </c>
       <c r="N15" s="10">
-        <f t="shared" ref="N15:N26" si="62">+AE15-SUM(K15:M15)</f>
+        <f t="shared" ref="N15:N26" si="63">+AE15-SUM(K15:M15)</f>
         <v>1596</v>
       </c>
       <c r="O15" s="10">
@@ -3266,7 +3275,7 @@
         <v>8451</v>
       </c>
       <c r="F16" s="19">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>8631</v>
       </c>
       <c r="G16" s="19">
@@ -3282,7 +3291,7 @@
         <v>9393</v>
       </c>
       <c r="J16" s="19">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>10245</v>
       </c>
       <c r="K16" s="19">
@@ -3298,7 +3307,7 @@
         <v>10365</v>
       </c>
       <c r="N16" s="19">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>11271</v>
       </c>
       <c r="O16" s="19">
@@ -3355,35 +3364,35 @@
         <v>49543.607600000003</v>
       </c>
       <c r="AH16" s="12">
-        <f t="shared" ref="AH16:AO16" si="63">+AH11</f>
+        <f t="shared" ref="AH16:AO16" si="64">+AH11</f>
         <v>53901.786867999996</v>
       </c>
       <c r="AI16" s="12">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>58440.927742440013</v>
       </c>
       <c r="AJ16" s="12">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>63004.939473085207</v>
       </c>
       <c r="AK16" s="12">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>67421.860812744533</v>
       </c>
       <c r="AL16" s="12">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>72180.462325567234</v>
       </c>
       <c r="AM16" s="12">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>77309.444764395885</v>
       </c>
       <c r="AN16" s="12">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>82840.068260819011</v>
       </c>
       <c r="AO16" s="12">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>88806.389741553445</v>
       </c>
     </row>
@@ -3401,7 +3410,7 @@
         <v>3792</v>
       </c>
       <c r="F17" s="10">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>3880</v>
       </c>
       <c r="G17" s="10">
@@ -3414,7 +3423,7 @@
         <v>4174</v>
       </c>
       <c r="J17" s="10">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>4468</v>
       </c>
       <c r="K17" s="10">
@@ -3427,7 +3436,7 @@
         <v>4606</v>
       </c>
       <c r="N17" s="10">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>5034</v>
       </c>
       <c r="O17" s="10">
@@ -3446,43 +3455,43 @@
         <v>19738</v>
       </c>
       <c r="AF17" s="1">
-        <f t="shared" ref="AF17:AO17" si="64">+AF$16*(AE17/AE$16)</f>
+        <f t="shared" ref="AF17:AO17" si="65">+AF$16*(AE17/AE$16)</f>
         <v>18898.274771926655</v>
       </c>
       <c r="AG17" s="1">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v>22082.280887200799</v>
       </c>
       <c r="AH17" s="1">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v>24024.782521917263</v>
       </c>
       <c r="AI17" s="1">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v>26047.941283088276</v>
       </c>
       <c r="AJ17" s="1">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v>28082.185333749345</v>
       </c>
       <c r="AK17" s="1">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v>30050.869133816996</v>
       </c>
       <c r="AL17" s="1">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v>32171.844580029949</v>
       </c>
       <c r="AM17" s="1">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v>34457.90400053397</v>
       </c>
       <c r="AN17" s="1">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v>36922.98047448392</v>
       </c>
       <c r="AO17" s="1">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v>39582.253651855797</v>
       </c>
     </row>
@@ -3500,7 +3509,7 @@
         <v>2222</v>
       </c>
       <c r="F18" s="10">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>2135</v>
       </c>
       <c r="G18" s="10">
@@ -3513,7 +3522,7 @@
         <v>2259</v>
       </c>
       <c r="J18" s="10">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>2302</v>
       </c>
       <c r="K18" s="10">
@@ -3526,7 +3535,7 @@
         <v>2226</v>
       </c>
       <c r="N18" s="10">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>2370</v>
       </c>
       <c r="O18" s="10">
@@ -3545,43 +3554,43 @@
         <v>9042</v>
       </c>
       <c r="AF18" s="1">
-        <f t="shared" ref="AF18:AO18" si="65">+AF$16*(AE18/AE$16)</f>
+        <f t="shared" ref="AF18:AO18" si="66">+AF$16*(AE18/AE$16)</f>
         <v>8657.3209285520734</v>
       </c>
       <c r="AG18" s="1">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v>10115.91771111914</v>
       </c>
       <c r="AH18" s="1">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v>11005.779894780415</v>
       </c>
       <c r="AI18" s="1">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v>11932.591198788334</v>
       </c>
       <c r="AJ18" s="1">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v>12864.480686379649</v>
       </c>
       <c r="AK18" s="1">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v>13766.336949436276</v>
       </c>
       <c r="AL18" s="1">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v>14737.958186879659</v>
       </c>
       <c r="AM18" s="1">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v>15785.204578621342</v>
       </c>
       <c r="AN18" s="1">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v>16914.458883893178</v>
       </c>
       <c r="AO18" s="1">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v>18132.674917422235</v>
       </c>
     </row>
@@ -3599,7 +3608,7 @@
         <v>618</v>
       </c>
       <c r="F19" s="10">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>628</v>
       </c>
       <c r="G19" s="10">
@@ -3612,7 +3621,7 @@
         <v>664</v>
       </c>
       <c r="J19" s="10">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>761</v>
       </c>
       <c r="K19" s="10">
@@ -3625,7 +3634,7 @@
         <v>771</v>
       </c>
       <c r="N19" s="10">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>910</v>
       </c>
       <c r="O19" s="10">
@@ -3644,43 +3653,43 @@
         <v>3110</v>
       </c>
       <c r="AF19" s="1">
-        <f t="shared" ref="AF19:AO19" si="66">+AF$16*(AE19/AE$16)</f>
+        <f t="shared" ref="AF19:AO19" si="67">+AF$16*(AE19/AE$16)</f>
         <v>2977.6894589467979</v>
       </c>
       <c r="AG19" s="1">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>3479.3744836961432</v>
       </c>
       <c r="AH19" s="1">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>3785.4429852651065</v>
       </c>
       <c r="AI19" s="1">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>4104.2201535314889</v>
       </c>
       <c r="AJ19" s="1">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>4424.7439653440297</v>
       </c>
       <c r="AK19" s="1">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>4734.937835959613</v>
       </c>
       <c r="AL19" s="1">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>5069.127401149718</v>
       </c>
       <c r="AM19" s="1">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>5429.3282724521541</v>
       </c>
       <c r="AN19" s="1">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>5817.7358027989139</v>
       </c>
       <c r="AO19" s="1">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>6236.7417599185083</v>
       </c>
     </row>
@@ -3698,7 +3707,7 @@
         <v>-4</v>
       </c>
       <c r="F20" s="10">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>578</v>
       </c>
       <c r="G20" s="10">
@@ -3711,7 +3720,7 @@
         <v>74</v>
       </c>
       <c r="J20" s="10">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>133</v>
       </c>
       <c r="K20" s="10">
@@ -3724,7 +3733,7 @@
         <v>0</v>
       </c>
       <c r="N20" s="10">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>39</v>
       </c>
       <c r="O20" s="10">
@@ -3743,43 +3752,43 @@
         <v>39</v>
       </c>
       <c r="AF20" s="1">
-        <f t="shared" ref="AF20:AO20" si="67">+AF$16*(AE20/AE$16)</f>
+        <f t="shared" ref="AF20:AO20" si="68">+AF$16*(AE20/AE$16)</f>
         <v>37.340800289043443</v>
       </c>
       <c r="AG20" s="1">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v>43.632027287507903</v>
       </c>
       <c r="AH20" s="1">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v>47.470185345768215</v>
       </c>
       <c r="AI20" s="1">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v>51.467712536246964</v>
       </c>
       <c r="AJ20" s="1">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v>55.487142973767568</v>
       </c>
       <c r="AK20" s="1">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v>59.377033955763629</v>
       </c>
       <c r="AL20" s="1">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v>63.567835577118643</v>
       </c>
       <c r="AM20" s="1">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v>68.084823995380717</v>
       </c>
       <c r="AN20" s="1">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v>72.955529359857778</v>
       </c>
       <c r="AO20" s="1">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v>78.209944899299629</v>
       </c>
     </row>
@@ -3800,7 +3809,7 @@
         <v>1823</v>
       </c>
       <c r="F21" s="10">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>1410</v>
       </c>
       <c r="G21" s="10">
@@ -3816,7 +3825,7 @@
         <v>2222</v>
       </c>
       <c r="J21" s="10">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>2581</v>
       </c>
       <c r="K21" s="10">
@@ -3832,7 +3841,7 @@
         <v>2762</v>
       </c>
       <c r="N21" s="10">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>2918</v>
       </c>
       <c r="O21" s="10">
@@ -3856,43 +3865,43 @@
         <v>12355</v>
       </c>
       <c r="AF21" s="1">
-        <f t="shared" ref="AF21:AN21" si="68">+AF16-SUM(AF17:AF20)</f>
+        <f t="shared" ref="AF21:AN21" si="69">+AF16-SUM(AF17:AF20)</f>
         <v>11829.374040285431</v>
       </c>
       <c r="AG21" s="1">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v>13822.402490696411</v>
       </c>
       <c r="AH21" s="1">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v>15038.311280691443</v>
       </c>
       <c r="AI21" s="1">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v>16304.707394495665</v>
       </c>
       <c r="AJ21" s="1">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v>17578.042344638416</v>
       </c>
       <c r="AK21" s="1">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v>18810.339859575877</v>
       </c>
       <c r="AL21" s="1">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v>20137.964321930798</v>
       </c>
       <c r="AM21" s="1">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v>21568.923088793039</v>
       </c>
       <c r="AN21" s="1">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v>23111.937570283138</v>
       </c>
       <c r="AO21" s="1">
-        <f t="shared" ref="AO21" si="69">+AO16-SUM(AO17:AO20)</f>
+        <f t="shared" ref="AO21" si="70">+AO16-SUM(AO17:AO20)</f>
         <v>24776.509467457603</v>
       </c>
     </row>
@@ -3910,7 +3919,7 @@
         <v>-172</v>
       </c>
       <c r="F22" s="10">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>-173</v>
       </c>
       <c r="G22" s="10">
@@ -3923,7 +3932,7 @@
         <v>-168</v>
       </c>
       <c r="J22" s="10">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>-179</v>
       </c>
       <c r="K22" s="10">
@@ -3936,7 +3945,7 @@
         <v>-168</v>
       </c>
       <c r="N22" s="10">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>-170</v>
       </c>
       <c r="O22" s="10">
@@ -3955,43 +3964,43 @@
         <v>-664</v>
       </c>
       <c r="AF22" s="1">
-        <f>+AE50*$AR$30*4</f>
+        <f t="shared" ref="AF22:AO22" si="71">+AE50*$AR$30*4</f>
         <v>-625.27920000000006</v>
       </c>
       <c r="AG22" s="1">
-        <f>+AF50*$AR$30*4</f>
+        <f t="shared" si="71"/>
         <v>-594.01524000000006</v>
       </c>
       <c r="AH22" s="1">
-        <f>+AG50*$AR$30*4</f>
+        <f t="shared" si="71"/>
         <v>-564.31447800000001</v>
       </c>
       <c r="AI22" s="1">
-        <f>+AH50*$AR$30*4</f>
+        <f t="shared" si="71"/>
         <v>-536.09875409999995</v>
       </c>
       <c r="AJ22" s="1">
-        <f>+AI50*$AR$30*4</f>
+        <f t="shared" si="71"/>
         <v>-509.29381639499991</v>
       </c>
       <c r="AK22" s="1">
-        <f>+AJ50*$AR$30*4</f>
+        <f t="shared" si="71"/>
         <v>-483.82912557524992</v>
       </c>
       <c r="AL22" s="1">
-        <f>+AK50*$AR$30*4</f>
+        <f t="shared" si="71"/>
         <v>-459.63766929648739</v>
       </c>
       <c r="AM22" s="1">
-        <f>+AL50*$AR$30*4</f>
+        <f t="shared" si="71"/>
         <v>-436.65578583166297</v>
       </c>
       <c r="AN22" s="1">
-        <f>+AM50*$AR$30*4</f>
+        <f t="shared" si="71"/>
         <v>-414.82299654007983</v>
       </c>
       <c r="AO22" s="1">
-        <f>+AN50*$AR$30*4</f>
+        <f t="shared" si="71"/>
         <v>-394.08184671307589</v>
       </c>
     </row>
@@ -4009,7 +4018,7 @@
         <v>106</v>
       </c>
       <c r="F23" s="10">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>183</v>
       </c>
       <c r="G23" s="10">
@@ -4022,7 +4031,7 @@
         <v>226</v>
       </c>
       <c r="J23" s="10">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>194</v>
       </c>
       <c r="K23" s="10">
@@ -4035,7 +4044,7 @@
         <v>358</v>
       </c>
       <c r="N23" s="10">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>223</v>
       </c>
       <c r="O23" s="10">
@@ -4058,39 +4067,39 @@
         <v>972</v>
       </c>
       <c r="AG23" s="1">
-        <f t="shared" ref="AG23:AO23" si="70">+AF23</f>
+        <f t="shared" ref="AG23:AO23" si="72">+AF23</f>
         <v>972</v>
       </c>
       <c r="AH23" s="1">
-        <f t="shared" si="70"/>
+        <f t="shared" si="72"/>
         <v>972</v>
       </c>
       <c r="AI23" s="1">
-        <f t="shared" si="70"/>
+        <f t="shared" si="72"/>
         <v>972</v>
       </c>
       <c r="AJ23" s="1">
-        <f t="shared" si="70"/>
+        <f t="shared" si="72"/>
         <v>972</v>
       </c>
       <c r="AK23" s="1">
-        <f t="shared" si="70"/>
+        <f t="shared" si="72"/>
         <v>972</v>
       </c>
       <c r="AL23" s="1">
-        <f t="shared" si="70"/>
+        <f t="shared" si="72"/>
         <v>972</v>
       </c>
       <c r="AM23" s="1">
-        <f t="shared" si="70"/>
+        <f t="shared" si="72"/>
         <v>972</v>
       </c>
       <c r="AN23" s="1">
-        <f t="shared" si="70"/>
+        <f t="shared" si="72"/>
         <v>972</v>
       </c>
       <c r="AO23" s="1">
-        <f t="shared" si="70"/>
+        <f t="shared" si="72"/>
         <v>972</v>
       </c>
     </row>
@@ -4111,7 +4120,7 @@
         <v>1757</v>
       </c>
       <c r="F24" s="10">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>1420</v>
       </c>
       <c r="G24" s="10">
@@ -4126,7 +4135,7 @@
         <v>2280</v>
       </c>
       <c r="J24" s="10">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>2596</v>
       </c>
       <c r="K24" s="10">
@@ -4142,7 +4151,7 @@
         <v>2952</v>
       </c>
       <c r="N24" s="10">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>2971</v>
       </c>
       <c r="O24" s="10">
@@ -4166,43 +4175,43 @@
         <v>12663</v>
       </c>
       <c r="AF24" s="1">
-        <f t="shared" ref="AF24:AN24" si="71">+AF21+SUM(AF22:AF23)</f>
+        <f t="shared" ref="AF24:AN24" si="73">+AF21+SUM(AF22:AF23)</f>
         <v>12176.09484028543</v>
       </c>
       <c r="AG24" s="1">
-        <f t="shared" si="71"/>
+        <f t="shared" si="73"/>
         <v>14200.387250696411</v>
       </c>
       <c r="AH24" s="1">
-        <f t="shared" si="71"/>
+        <f t="shared" si="73"/>
         <v>15445.996802691443</v>
       </c>
       <c r="AI24" s="1">
-        <f t="shared" si="71"/>
+        <f t="shared" si="73"/>
         <v>16740.608640395665</v>
       </c>
       <c r="AJ24" s="1">
-        <f t="shared" si="71"/>
+        <f t="shared" si="73"/>
         <v>18040.748528243417</v>
       </c>
       <c r="AK24" s="1">
-        <f t="shared" si="71"/>
+        <f t="shared" si="73"/>
         <v>19298.510734000629</v>
       </c>
       <c r="AL24" s="1">
-        <f t="shared" si="71"/>
+        <f t="shared" si="73"/>
         <v>20650.32665263431</v>
       </c>
       <c r="AM24" s="1">
-        <f t="shared" si="71"/>
+        <f t="shared" si="73"/>
         <v>22104.267302961376</v>
       </c>
       <c r="AN24" s="1">
-        <f t="shared" si="71"/>
+        <f t="shared" si="73"/>
         <v>23669.11457374306</v>
       </c>
       <c r="AO24" s="1">
-        <f t="shared" ref="AO24" si="72">+AO21+SUM(AO22:AO23)</f>
+        <f t="shared" ref="AO24" si="74">+AO21+SUM(AO22:AO23)</f>
         <v>25354.427620744525</v>
       </c>
     </row>
@@ -4220,7 +4229,7 @@
         <v>-22</v>
       </c>
       <c r="F25" s="10">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>209</v>
       </c>
       <c r="G25" s="10">
@@ -4233,7 +4242,7 @@
         <v>-171</v>
       </c>
       <c r="J25" s="10">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>319</v>
       </c>
       <c r="K25" s="10">
@@ -4246,7 +4255,7 @@
         <v>-286</v>
       </c>
       <c r="N25" s="10">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>-6088</v>
       </c>
       <c r="O25" s="10">
@@ -4277,31 +4286,31 @@
         <v>-8687.2296634895738</v>
       </c>
       <c r="AI25" s="1">
-        <f t="shared" ref="AF25:AO25" si="73">+AI24*(AH25/AH24)</f>
+        <f t="shared" ref="AI25:AO25" si="75">+AI24*(AH25/AH24)</f>
         <v>-9415.3529761429327</v>
       </c>
       <c r="AJ25" s="1">
-        <f t="shared" si="73"/>
+        <f t="shared" si="75"/>
         <v>-10146.585407735107</v>
       </c>
       <c r="AK25" s="1">
-        <f t="shared" si="73"/>
+        <f t="shared" si="75"/>
         <v>-10853.983530565625</v>
       </c>
       <c r="AL25" s="1">
-        <f t="shared" si="73"/>
+        <f t="shared" si="75"/>
         <v>-11614.279903661185</v>
       </c>
       <c r="AM25" s="1">
-        <f t="shared" si="73"/>
+        <f t="shared" si="75"/>
         <v>-12432.013877571741</v>
       </c>
       <c r="AN25" s="1">
-        <f t="shared" si="73"/>
+        <f t="shared" si="75"/>
         <v>-13312.124614561961</v>
       </c>
       <c r="AO25" s="1">
-        <f t="shared" si="73"/>
+        <f t="shared" si="75"/>
         <v>-14259.988432041582</v>
       </c>
     </row>
@@ -4322,7 +4331,7 @@
         <v>1735</v>
       </c>
       <c r="F26" s="10">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>1629</v>
       </c>
       <c r="G26" s="10">
@@ -4338,7 +4347,7 @@
         <v>2109</v>
       </c>
       <c r="J26" s="10">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>2915</v>
       </c>
       <c r="K26" s="10">
@@ -4354,7 +4363,7 @@
         <v>2666</v>
       </c>
       <c r="N26" s="10">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>-3117</v>
       </c>
       <c r="O26" s="10">
@@ -4378,843 +4387,843 @@
         <v>5541</v>
       </c>
       <c r="AF26" s="1">
-        <f t="shared" ref="AF26:AN26" si="74">+AF24+AF25</f>
+        <f t="shared" ref="AF26:AN26" si="76">+AF24+AF25</f>
         <v>5327.9429448015135</v>
       </c>
       <c r="AG26" s="1">
-        <f t="shared" si="74"/>
+        <f t="shared" si="76"/>
         <v>6213.720742012857</v>
       </c>
       <c r="AH26" s="1">
-        <f t="shared" si="74"/>
+        <f t="shared" si="76"/>
         <v>6758.7671392018692</v>
       </c>
       <c r="AI26" s="1">
-        <f t="shared" si="74"/>
+        <f t="shared" si="76"/>
         <v>7325.2556642527325</v>
       </c>
       <c r="AJ26" s="1">
-        <f t="shared" si="74"/>
+        <f t="shared" si="76"/>
         <v>7894.1631205083104</v>
       </c>
       <c r="AK26" s="1">
-        <f t="shared" si="74"/>
+        <f t="shared" si="76"/>
         <v>8444.5272034350037</v>
       </c>
       <c r="AL26" s="1">
-        <f t="shared" si="74"/>
+        <f t="shared" si="76"/>
         <v>9036.0467489731254</v>
       </c>
       <c r="AM26" s="1">
-        <f t="shared" si="74"/>
+        <f t="shared" si="76"/>
         <v>9672.2534253896356</v>
       </c>
       <c r="AN26" s="1">
-        <f t="shared" si="74"/>
+        <f t="shared" si="76"/>
         <v>10356.989959181099</v>
       </c>
       <c r="AO26" s="1">
-        <f t="shared" ref="AO26" si="75">+AO24+AO25</f>
+        <f t="shared" ref="AO26" si="77">+AO24+AO25</f>
         <v>11094.439188702943</v>
       </c>
       <c r="AP26" s="1">
-        <f>+AO26*(1+$AR$31)</f>
+        <f t="shared" ref="AP26:BU26" si="78">+AO26*(1+$AR$31)</f>
         <v>11205.383580589973</v>
       </c>
       <c r="AQ26" s="1">
-        <f>+AP26*(1+$AR$31)</f>
+        <f t="shared" si="78"/>
         <v>11317.437416395873</v>
       </c>
       <c r="AR26" s="1">
-        <f>+AQ26*(1+$AR$31)</f>
+        <f t="shared" si="78"/>
         <v>11430.611790559831</v>
       </c>
       <c r="AS26" s="1">
-        <f>+AR26*(1+$AR$31)</f>
+        <f t="shared" si="78"/>
         <v>11544.91790846543</v>
       </c>
       <c r="AT26" s="1">
-        <f>+AS26*(1+$AR$31)</f>
+        <f t="shared" si="78"/>
         <v>11660.367087550085</v>
       </c>
       <c r="AU26" s="1">
-        <f>+AT26*(1+$AR$31)</f>
+        <f t="shared" si="78"/>
         <v>11776.970758425587</v>
       </c>
       <c r="AV26" s="1">
-        <f>+AU26*(1+$AR$31)</f>
+        <f t="shared" si="78"/>
         <v>11894.740466009842</v>
       </c>
       <c r="AW26" s="1">
-        <f>+AV26*(1+$AR$31)</f>
+        <f t="shared" si="78"/>
         <v>12013.687870669941</v>
       </c>
       <c r="AX26" s="1">
-        <f>+AW26*(1+$AR$31)</f>
+        <f t="shared" si="78"/>
         <v>12133.824749376641</v>
       </c>
       <c r="AY26" s="1">
-        <f>+AX26*(1+$AR$31)</f>
+        <f t="shared" si="78"/>
         <v>12255.162996870407</v>
       </c>
       <c r="AZ26" s="1">
-        <f>+AY26*(1+$AR$31)</f>
+        <f t="shared" si="78"/>
         <v>12377.714626839112</v>
       </c>
       <c r="BA26" s="1">
-        <f>+AZ26*(1+$AR$31)</f>
+        <f t="shared" si="78"/>
         <v>12501.491773107502</v>
       </c>
       <c r="BB26" s="1">
-        <f>+BA26*(1+$AR$31)</f>
+        <f t="shared" si="78"/>
         <v>12626.506690838578</v>
       </c>
       <c r="BC26" s="1">
-        <f>+BB26*(1+$AR$31)</f>
+        <f t="shared" si="78"/>
         <v>12752.771757746963</v>
       </c>
       <c r="BD26" s="1">
-        <f>+BC26*(1+$AR$31)</f>
+        <f t="shared" si="78"/>
         <v>12880.299475324433</v>
       </c>
       <c r="BE26" s="1">
-        <f>+BD26*(1+$AR$31)</f>
+        <f t="shared" si="78"/>
         <v>13009.102470077678</v>
       </c>
       <c r="BF26" s="1">
-        <f>+BE26*(1+$AR$31)</f>
+        <f t="shared" si="78"/>
         <v>13139.193494778456</v>
       </c>
       <c r="BG26" s="1">
-        <f>+BF26*(1+$AR$31)</f>
+        <f t="shared" si="78"/>
         <v>13270.585429726241</v>
       </c>
       <c r="BH26" s="1">
-        <f>+BG26*(1+$AR$31)</f>
+        <f t="shared" si="78"/>
         <v>13403.291284023504</v>
       </c>
       <c r="BI26" s="1">
-        <f>+BH26*(1+$AR$31)</f>
+        <f t="shared" si="78"/>
         <v>13537.324196863739</v>
       </c>
       <c r="BJ26" s="1">
-        <f>+BI26*(1+$AR$31)</f>
+        <f t="shared" si="78"/>
         <v>13672.697438832376</v>
       </c>
       <c r="BK26" s="1">
-        <f>+BJ26*(1+$AR$31)</f>
+        <f t="shared" si="78"/>
         <v>13809.4244132207</v>
       </c>
       <c r="BL26" s="1">
-        <f>+BK26*(1+$AR$31)</f>
+        <f t="shared" si="78"/>
         <v>13947.518657352908</v>
       </c>
       <c r="BM26" s="1">
-        <f>+BL26*(1+$AR$31)</f>
+        <f t="shared" si="78"/>
         <v>14086.993843926437</v>
       </c>
       <c r="BN26" s="1">
-        <f>+BM26*(1+$AR$31)</f>
+        <f t="shared" si="78"/>
         <v>14227.863782365701</v>
       </c>
       <c r="BO26" s="1">
-        <f>+BN26*(1+$AR$31)</f>
+        <f t="shared" si="78"/>
         <v>14370.142420189359</v>
       </c>
       <c r="BP26" s="1">
-        <f>+BO26*(1+$AR$31)</f>
+        <f t="shared" si="78"/>
         <v>14513.843844391253</v>
       </c>
       <c r="BQ26" s="1">
-        <f>+BP26*(1+$AR$31)</f>
+        <f t="shared" si="78"/>
         <v>14658.982282835166</v>
       </c>
       <c r="BR26" s="1">
-        <f>+BQ26*(1+$AR$31)</f>
+        <f t="shared" si="78"/>
         <v>14805.572105663518</v>
       </c>
       <c r="BS26" s="1">
-        <f>+BR26*(1+$AR$31)</f>
+        <f t="shared" si="78"/>
         <v>14953.627826720152</v>
       </c>
       <c r="BT26" s="1">
-        <f>+BS26*(1+$AR$31)</f>
+        <f t="shared" si="78"/>
         <v>15103.164104987354</v>
       </c>
       <c r="BU26" s="1">
-        <f>+BT26*(1+$AR$31)</f>
+        <f t="shared" si="78"/>
         <v>15254.195746037229</v>
       </c>
       <c r="BV26" s="1">
-        <f>+BU26*(1+$AR$31)</f>
+        <f t="shared" ref="BV26:DA26" si="79">+BU26*(1+$AR$31)</f>
         <v>15406.737703497602</v>
       </c>
       <c r="BW26" s="1">
-        <f>+BV26*(1+$AR$31)</f>
+        <f t="shared" si="79"/>
         <v>15560.805080532578</v>
       </c>
       <c r="BX26" s="1">
-        <f>+BW26*(1+$AR$31)</f>
+        <f t="shared" si="79"/>
         <v>15716.413131337904</v>
       </c>
       <c r="BY26" s="1">
-        <f>+BX26*(1+$AR$31)</f>
+        <f t="shared" si="79"/>
         <v>15873.577262651283</v>
       </c>
       <c r="BZ26" s="1">
-        <f>+BY26*(1+$AR$31)</f>
+        <f t="shared" si="79"/>
         <v>16032.313035277795</v>
       </c>
       <c r="CA26" s="1">
-        <f>+BZ26*(1+$AR$31)</f>
+        <f t="shared" si="79"/>
         <v>16192.636165630573</v>
       </c>
       <c r="CB26" s="1">
-        <f>+CA26*(1+$AR$31)</f>
+        <f t="shared" si="79"/>
         <v>16354.562527286878</v>
       </c>
       <c r="CC26" s="1">
-        <f>+CB26*(1+$AR$31)</f>
+        <f t="shared" si="79"/>
         <v>16518.108152559747</v>
       </c>
       <c r="CD26" s="1">
-        <f>+CC26*(1+$AR$31)</f>
+        <f t="shared" si="79"/>
         <v>16683.289234085347</v>
       </c>
       <c r="CE26" s="1">
-        <f>+CD26*(1+$AR$31)</f>
+        <f t="shared" si="79"/>
         <v>16850.122126426202</v>
       </c>
       <c r="CF26" s="1">
-        <f>+CE26*(1+$AR$31)</f>
+        <f t="shared" si="79"/>
         <v>17018.623347690464</v>
       </c>
       <c r="CG26" s="1">
-        <f>+CF26*(1+$AR$31)</f>
+        <f t="shared" si="79"/>
         <v>17188.809581167367</v>
       </c>
       <c r="CH26" s="1">
-        <f>+CG26*(1+$AR$31)</f>
+        <f t="shared" si="79"/>
         <v>17360.697676979042</v>
       </c>
       <c r="CI26" s="1">
-        <f>+CH26*(1+$AR$31)</f>
+        <f t="shared" si="79"/>
         <v>17534.304653748834</v>
       </c>
       <c r="CJ26" s="1">
-        <f>+CI26*(1+$AR$31)</f>
+        <f t="shared" si="79"/>
         <v>17709.647700286321</v>
       </c>
       <c r="CK26" s="1">
-        <f>+CJ26*(1+$AR$31)</f>
+        <f t="shared" si="79"/>
         <v>17886.744177289183</v>
       </c>
       <c r="CL26" s="1">
-        <f>+CK26*(1+$AR$31)</f>
+        <f t="shared" si="79"/>
         <v>18065.611619062074</v>
       </c>
       <c r="CM26" s="1">
-        <f>+CL26*(1+$AR$31)</f>
+        <f t="shared" si="79"/>
         <v>18246.267735252695</v>
       </c>
       <c r="CN26" s="1">
-        <f>+CM26*(1+$AR$31)</f>
+        <f t="shared" si="79"/>
         <v>18428.730412605222</v>
       </c>
       <c r="CO26" s="1">
-        <f>+CN26*(1+$AR$31)</f>
+        <f t="shared" si="79"/>
         <v>18613.017716731276</v>
       </c>
       <c r="CP26" s="1">
-        <f>+CO26*(1+$AR$31)</f>
+        <f t="shared" si="79"/>
         <v>18799.147893898589</v>
       </c>
       <c r="CQ26" s="1">
-        <f>+CP26*(1+$AR$31)</f>
+        <f t="shared" si="79"/>
         <v>18987.139372837577</v>
       </c>
       <c r="CR26" s="1">
-        <f>+CQ26*(1+$AR$31)</f>
+        <f t="shared" si="79"/>
         <v>19177.010766565953</v>
       </c>
       <c r="CS26" s="1">
-        <f>+CR26*(1+$AR$31)</f>
+        <f t="shared" si="79"/>
         <v>19368.780874231612</v>
       </c>
       <c r="CT26" s="1">
-        <f>+CS26*(1+$AR$31)</f>
+        <f t="shared" si="79"/>
         <v>19562.468682973929</v>
       </c>
       <c r="CU26" s="1">
-        <f>+CT26*(1+$AR$31)</f>
+        <f t="shared" si="79"/>
         <v>19758.093369803668</v>
       </c>
       <c r="CV26" s="1">
-        <f>+CU26*(1+$AR$31)</f>
+        <f t="shared" si="79"/>
         <v>19955.674303501706</v>
       </c>
       <c r="CW26" s="1">
-        <f>+CV26*(1+$AR$31)</f>
+        <f t="shared" si="79"/>
         <v>20155.231046536723</v>
       </c>
       <c r="CX26" s="1">
-        <f>+CW26*(1+$AR$31)</f>
+        <f t="shared" si="79"/>
         <v>20356.783357002088</v>
       </c>
       <c r="CY26" s="1">
-        <f>+CX26*(1+$AR$31)</f>
+        <f t="shared" si="79"/>
         <v>20560.35119057211</v>
       </c>
       <c r="CZ26" s="1">
-        <f>+CY26*(1+$AR$31)</f>
+        <f t="shared" si="79"/>
         <v>20765.954702477829</v>
       </c>
       <c r="DA26" s="1">
-        <f>+CZ26*(1+$AR$31)</f>
+        <f t="shared" si="79"/>
         <v>20973.614249502607</v>
       </c>
       <c r="DB26" s="1">
-        <f>+DA26*(1+$AR$31)</f>
+        <f t="shared" ref="DB26:EG26" si="80">+DA26*(1+$AR$31)</f>
         <v>21183.350391997632</v>
       </c>
       <c r="DC26" s="1">
-        <f>+DB26*(1+$AR$31)</f>
+        <f t="shared" si="80"/>
         <v>21395.183895917609</v>
       </c>
       <c r="DD26" s="1">
-        <f>+DC26*(1+$AR$31)</f>
+        <f t="shared" si="80"/>
         <v>21609.135734876785</v>
       </c>
       <c r="DE26" s="1">
-        <f>+DD26*(1+$AR$31)</f>
+        <f t="shared" si="80"/>
         <v>21825.227092225552</v>
       </c>
       <c r="DF26" s="1">
-        <f>+DE26*(1+$AR$31)</f>
+        <f t="shared" si="80"/>
         <v>22043.479363147806</v>
       </c>
       <c r="DG26" s="1">
-        <f>+DF26*(1+$AR$31)</f>
+        <f t="shared" si="80"/>
         <v>22263.914156779283</v>
       </c>
       <c r="DH26" s="1">
-        <f>+DG26*(1+$AR$31)</f>
+        <f t="shared" si="80"/>
         <v>22486.553298347077</v>
       </c>
       <c r="DI26" s="1">
-        <f>+DH26*(1+$AR$31)</f>
+        <f t="shared" si="80"/>
         <v>22711.418831330546</v>
       </c>
       <c r="DJ26" s="1">
-        <f>+DI26*(1+$AR$31)</f>
+        <f t="shared" si="80"/>
         <v>22938.533019643852</v>
       </c>
       <c r="DK26" s="1">
-        <f>+DJ26*(1+$AR$31)</f>
+        <f t="shared" si="80"/>
         <v>23167.918349840289</v>
       </c>
       <c r="DL26" s="1">
-        <f>+DK26*(1+$AR$31)</f>
+        <f t="shared" si="80"/>
         <v>23399.597533338692</v>
       </c>
       <c r="DM26" s="1">
-        <f>+DL26*(1+$AR$31)</f>
+        <f t="shared" si="80"/>
         <v>23633.593508672078</v>
       </c>
       <c r="DN26" s="1">
-        <f>+DM26*(1+$AR$31)</f>
+        <f t="shared" si="80"/>
         <v>23869.9294437588</v>
       </c>
       <c r="DO26" s="1">
-        <f>+DN26*(1+$AR$31)</f>
+        <f t="shared" si="80"/>
         <v>24108.628738196388</v>
       </c>
       <c r="DP26" s="1">
-        <f>+DO26*(1+$AR$31)</f>
+        <f t="shared" si="80"/>
         <v>24349.715025578353</v>
       </c>
       <c r="DQ26" s="1">
-        <f>+DP26*(1+$AR$31)</f>
+        <f t="shared" si="80"/>
         <v>24593.212175834138</v>
       </c>
       <c r="DR26" s="1">
-        <f>+DQ26*(1+$AR$31)</f>
+        <f t="shared" si="80"/>
         <v>24839.14429759248</v>
       </c>
       <c r="DS26" s="1">
-        <f>+DR26*(1+$AR$31)</f>
+        <f t="shared" si="80"/>
         <v>25087.535740568404</v>
       </c>
       <c r="DT26" s="1">
-        <f>+DS26*(1+$AR$31)</f>
+        <f t="shared" si="80"/>
         <v>25338.411097974087</v>
       </c>
       <c r="DU26" s="1">
-        <f>+DT26*(1+$AR$31)</f>
+        <f t="shared" si="80"/>
         <v>25591.795208953827</v>
       </c>
       <c r="DV26" s="1">
-        <f>+DU26*(1+$AR$31)</f>
+        <f t="shared" si="80"/>
         <v>25847.713161043364</v>
       </c>
       <c r="DW26" s="1">
-        <f>+DV26*(1+$AR$31)</f>
+        <f t="shared" si="80"/>
         <v>26106.190292653799</v>
       </c>
       <c r="DX26" s="1">
-        <f>+DW26*(1+$AR$31)</f>
+        <f t="shared" si="80"/>
         <v>26367.252195580339</v>
       </c>
       <c r="DY26" s="1">
-        <f>+DX26*(1+$AR$31)</f>
+        <f t="shared" si="80"/>
         <v>26630.924717536142</v>
       </c>
       <c r="DZ26" s="1">
-        <f>+DY26*(1+$AR$31)</f>
+        <f t="shared" si="80"/>
         <v>26897.233964711504</v>
       </c>
       <c r="EA26" s="1">
-        <f>+DZ26*(1+$AR$31)</f>
+        <f t="shared" si="80"/>
         <v>27166.20630435862</v>
       </c>
       <c r="EB26" s="1">
-        <f>+EA26*(1+$AR$31)</f>
+        <f t="shared" si="80"/>
         <v>27437.868367402207</v>
       </c>
       <c r="EC26" s="1">
-        <f>+EB26*(1+$AR$31)</f>
+        <f t="shared" si="80"/>
         <v>27712.247051076229</v>
       </c>
       <c r="ED26" s="1">
-        <f>+EC26*(1+$AR$31)</f>
+        <f t="shared" si="80"/>
         <v>27989.369521586992</v>
       </c>
       <c r="EE26" s="1">
-        <f>+ED26*(1+$AR$31)</f>
+        <f t="shared" si="80"/>
         <v>28269.263216802861</v>
       </c>
       <c r="EF26" s="1">
-        <f>+EE26*(1+$AR$31)</f>
+        <f t="shared" si="80"/>
         <v>28551.955848970891</v>
       </c>
       <c r="EG26" s="1">
-        <f>+EF26*(1+$AR$31)</f>
+        <f t="shared" si="80"/>
         <v>28837.475407460599</v>
       </c>
       <c r="EH26" s="1">
-        <f>+EG26*(1+$AR$31)</f>
+        <f t="shared" ref="EH26:FM26" si="81">+EG26*(1+$AR$31)</f>
         <v>29125.850161535207</v>
       </c>
       <c r="EI26" s="1">
-        <f>+EH26*(1+$AR$31)</f>
+        <f t="shared" si="81"/>
         <v>29417.10866315056</v>
       </c>
       <c r="EJ26" s="1">
-        <f>+EI26*(1+$AR$31)</f>
+        <f t="shared" si="81"/>
         <v>29711.279749782065</v>
       </c>
       <c r="EK26" s="1">
-        <f>+EJ26*(1+$AR$31)</f>
+        <f t="shared" si="81"/>
         <v>30008.392547279887</v>
       </c>
       <c r="EL26" s="1">
-        <f>+EK26*(1+$AR$31)</f>
+        <f t="shared" si="81"/>
         <v>30308.476472752685</v>
       </c>
       <c r="EM26" s="1">
-        <f>+EL26*(1+$AR$31)</f>
+        <f t="shared" si="81"/>
         <v>30611.561237480211</v>
       </c>
       <c r="EN26" s="1">
-        <f>+EM26*(1+$AR$31)</f>
+        <f t="shared" si="81"/>
         <v>30917.676849855015</v>
       </c>
       <c r="EO26" s="1">
-        <f>+EN26*(1+$AR$31)</f>
+        <f t="shared" si="81"/>
         <v>31226.853618353565</v>
       </c>
       <c r="EP26" s="1">
-        <f>+EO26*(1+$AR$31)</f>
+        <f t="shared" si="81"/>
         <v>31539.122154537101</v>
       </c>
       <c r="EQ26" s="1">
-        <f>+EP26*(1+$AR$31)</f>
+        <f t="shared" si="81"/>
         <v>31854.513376082472</v>
       </c>
       <c r="ER26" s="1">
-        <f>+EQ26*(1+$AR$31)</f>
+        <f t="shared" si="81"/>
         <v>32173.058509843297</v>
       </c>
       <c r="ES26" s="1">
-        <f>+ER26*(1+$AR$31)</f>
+        <f t="shared" si="81"/>
         <v>32494.789094941731</v>
       </c>
       <c r="ET26" s="1">
-        <f>+ES26*(1+$AR$31)</f>
+        <f t="shared" si="81"/>
         <v>32819.736985891148</v>
       </c>
       <c r="EU26" s="1">
-        <f>+ET26*(1+$AR$31)</f>
+        <f t="shared" si="81"/>
         <v>33147.934355750062</v>
       </c>
       <c r="EV26" s="1">
-        <f>+EU26*(1+$AR$31)</f>
+        <f t="shared" si="81"/>
         <v>33479.413699307559</v>
       </c>
       <c r="EW26" s="1">
-        <f>+EV26*(1+$AR$31)</f>
+        <f t="shared" si="81"/>
         <v>33814.207836300637</v>
       </c>
       <c r="EX26" s="1">
-        <f>+EW26*(1+$AR$31)</f>
+        <f t="shared" si="81"/>
         <v>34152.349914663646</v>
       </c>
       <c r="EY26" s="1">
-        <f>+EX26*(1+$AR$31)</f>
+        <f t="shared" si="81"/>
         <v>34493.873413810281</v>
       </c>
       <c r="EZ26" s="1">
-        <f>+EY26*(1+$AR$31)</f>
+        <f t="shared" si="81"/>
         <v>34838.812147948382</v>
       </c>
       <c r="FA26" s="1">
-        <f>+EZ26*(1+$AR$31)</f>
+        <f t="shared" si="81"/>
         <v>35187.200269427864</v>
       </c>
       <c r="FB26" s="1">
-        <f>+FA26*(1+$AR$31)</f>
+        <f t="shared" si="81"/>
         <v>35539.072272122139</v>
       </c>
       <c r="FC26" s="1">
-        <f>+FB26*(1+$AR$31)</f>
+        <f t="shared" si="81"/>
         <v>35894.462994843358</v>
       </c>
       <c r="FD26" s="1">
-        <f>+FC26*(1+$AR$31)</f>
+        <f t="shared" si="81"/>
         <v>36253.407624791791</v>
       </c>
       <c r="FE26" s="1">
-        <f>+FD26*(1+$AR$31)</f>
+        <f t="shared" si="81"/>
         <v>36615.941701039708</v>
       </c>
       <c r="FF26" s="1">
-        <f>+FE26*(1+$AR$31)</f>
+        <f t="shared" si="81"/>
         <v>36982.101118050108</v>
       </c>
       <c r="FG26" s="1">
-        <f>+FF26*(1+$AR$31)</f>
+        <f t="shared" si="81"/>
         <v>37351.92212923061</v>
       </c>
       <c r="FH26" s="1">
-        <f>+FG26*(1+$AR$31)</f>
+        <f t="shared" si="81"/>
         <v>37725.441350522917</v>
       </c>
       <c r="FI26" s="1">
-        <f>+FH26*(1+$AR$31)</f>
+        <f t="shared" si="81"/>
         <v>38102.695764028147</v>
       </c>
       <c r="FJ26" s="1">
-        <f>+FI26*(1+$AR$31)</f>
+        <f t="shared" si="81"/>
         <v>38483.722721668426</v>
       </c>
       <c r="FK26" s="1">
-        <f>+FJ26*(1+$AR$31)</f>
+        <f t="shared" si="81"/>
         <v>38868.559948885108</v>
       </c>
       <c r="FL26" s="1">
-        <f>+FK26*(1+$AR$31)</f>
+        <f t="shared" si="81"/>
         <v>39257.245548373961</v>
       </c>
       <c r="FM26" s="1">
-        <f>+FL26*(1+$AR$31)</f>
+        <f t="shared" si="81"/>
         <v>39649.818003857705</v>
       </c>
       <c r="FN26" s="1">
-        <f>+FM26*(1+$AR$31)</f>
+        <f t="shared" ref="FN26:GS26" si="82">+FM26*(1+$AR$31)</f>
         <v>40046.316183896284</v>
       </c>
       <c r="FO26" s="1">
-        <f>+FN26*(1+$AR$31)</f>
+        <f t="shared" si="82"/>
         <v>40446.779345735245</v>
       </c>
       <c r="FP26" s="1">
-        <f>+FO26*(1+$AR$31)</f>
+        <f t="shared" si="82"/>
         <v>40851.247139192601</v>
       </c>
       <c r="FQ26" s="1">
-        <f>+FP26*(1+$AR$31)</f>
+        <f t="shared" si="82"/>
         <v>41259.75961058453</v>
       </c>
       <c r="FR26" s="1">
-        <f>+FQ26*(1+$AR$31)</f>
+        <f t="shared" si="82"/>
         <v>41672.357206690373</v>
       </c>
       <c r="FS26" s="1">
-        <f>+FR26*(1+$AR$31)</f>
+        <f t="shared" si="82"/>
         <v>42089.080778757278</v>
       </c>
       <c r="FT26" s="1">
-        <f>+FS26*(1+$AR$31)</f>
+        <f t="shared" si="82"/>
         <v>42509.971586544852</v>
       </c>
       <c r="FU26" s="1">
-        <f>+FT26*(1+$AR$31)</f>
+        <f t="shared" si="82"/>
         <v>42935.071302410302</v>
       </c>
       <c r="FV26" s="1">
-        <f>+FU26*(1+$AR$31)</f>
+        <f t="shared" si="82"/>
         <v>43364.422015434408</v>
       </c>
       <c r="FW26" s="1">
-        <f>+FV26*(1+$AR$31)</f>
+        <f t="shared" si="82"/>
         <v>43798.066235588754</v>
       </c>
       <c r="FX26" s="1">
-        <f>+FW26*(1+$AR$31)</f>
+        <f t="shared" si="82"/>
         <v>44236.046897944645</v>
       </c>
       <c r="FY26" s="1">
-        <f>+FX26*(1+$AR$31)</f>
+        <f t="shared" si="82"/>
         <v>44678.40736692409</v>
       </c>
       <c r="FZ26" s="1">
-        <f>+FY26*(1+$AR$31)</f>
+        <f t="shared" si="82"/>
         <v>45125.191440593328</v>
       </c>
       <c r="GA26" s="1">
-        <f>+FZ26*(1+$AR$31)</f>
+        <f t="shared" si="82"/>
         <v>45576.443354999261</v>
       </c>
       <c r="GB26" s="1">
-        <f>+GA26*(1+$AR$31)</f>
+        <f t="shared" si="82"/>
         <v>46032.207788549254</v>
       </c>
       <c r="GC26" s="1">
-        <f>+GB26*(1+$AR$31)</f>
+        <f t="shared" si="82"/>
         <v>46492.52986643475</v>
       </c>
       <c r="GD26" s="1">
-        <f>+GC26*(1+$AR$31)</f>
+        <f t="shared" si="82"/>
         <v>46957.455165099098</v>
       </c>
       <c r="GE26" s="1">
-        <f>+GD26*(1+$AR$31)</f>
+        <f t="shared" si="82"/>
         <v>47427.02971675009</v>
       </c>
       <c r="GF26" s="1">
-        <f>+GE26*(1+$AR$31)</f>
+        <f t="shared" si="82"/>
         <v>47901.300013917593</v>
       </c>
       <c r="GG26" s="1">
-        <f>+GF26*(1+$AR$31)</f>
+        <f t="shared" si="82"/>
         <v>48380.313014056766</v>
       </c>
       <c r="GH26" s="1">
-        <f>+GG26*(1+$AR$31)</f>
+        <f t="shared" si="82"/>
         <v>48864.116144197331</v>
       </c>
       <c r="GI26" s="1">
-        <f>+GH26*(1+$AR$31)</f>
+        <f t="shared" si="82"/>
         <v>49352.757305639301</v>
       </c>
       <c r="GJ26" s="1">
-        <f>+GI26*(1+$AR$31)</f>
+        <f t="shared" si="82"/>
         <v>49846.284878695697</v>
       </c>
       <c r="GK26" s="1">
-        <f>+GJ26*(1+$AR$31)</f>
+        <f t="shared" si="82"/>
         <v>50344.747727482652</v>
       </c>
       <c r="GL26" s="1">
-        <f>+GK26*(1+$AR$31)</f>
+        <f t="shared" si="82"/>
         <v>50848.195204757481</v>
       </c>
       <c r="GM26" s="1">
-        <f>+GL26*(1+$AR$31)</f>
+        <f t="shared" si="82"/>
         <v>51356.677156805054</v>
       </c>
       <c r="GN26" s="1">
-        <f>+GM26*(1+$AR$31)</f>
+        <f t="shared" si="82"/>
         <v>51870.243928373107</v>
       </c>
       <c r="GO26" s="1">
-        <f>+GN26*(1+$AR$31)</f>
+        <f t="shared" si="82"/>
         <v>52388.946367656841</v>
       </c>
       <c r="GP26" s="1">
-        <f>+GO26*(1+$AR$31)</f>
+        <f t="shared" si="82"/>
         <v>52912.83583133341</v>
       </c>
       <c r="GQ26" s="1">
-        <f>+GP26*(1+$AR$31)</f>
+        <f t="shared" si="82"/>
         <v>53441.964189646744</v>
       </c>
       <c r="GR26" s="1">
-        <f>+GQ26*(1+$AR$31)</f>
+        <f t="shared" si="82"/>
         <v>53976.383831543215</v>
       </c>
       <c r="GS26" s="1">
-        <f>+GR26*(1+$AR$31)</f>
+        <f t="shared" si="82"/>
         <v>54516.147669858648</v>
       </c>
       <c r="GT26" s="1">
-        <f>+GS26*(1+$AR$31)</f>
+        <f t="shared" ref="GT26:HY26" si="83">+GS26*(1+$AR$31)</f>
         <v>55061.309146557236</v>
       </c>
       <c r="GU26" s="1">
-        <f>+GT26*(1+$AR$31)</f>
+        <f t="shared" si="83"/>
         <v>55611.922238022809</v>
       </c>
       <c r="GV26" s="1">
-        <f>+GU26*(1+$AR$31)</f>
+        <f t="shared" si="83"/>
         <v>56168.041460403037</v>
       </c>
       <c r="GW26" s="1">
-        <f>+GV26*(1+$AR$31)</f>
+        <f t="shared" si="83"/>
         <v>56729.721875007068</v>
       </c>
       <c r="GX26" s="1">
-        <f>+GW26*(1+$AR$31)</f>
+        <f t="shared" si="83"/>
         <v>57297.019093757139</v>
       </c>
       <c r="GY26" s="1">
-        <f>+GX26*(1+$AR$31)</f>
+        <f t="shared" si="83"/>
         <v>57869.989284694711</v>
       </c>
       <c r="GZ26" s="1">
-        <f>+GY26*(1+$AR$31)</f>
+        <f t="shared" si="83"/>
         <v>58448.689177541659</v>
       </c>
       <c r="HA26" s="1">
-        <f>+GZ26*(1+$AR$31)</f>
+        <f t="shared" si="83"/>
         <v>59033.176069317073</v>
       </c>
       <c r="HB26" s="1">
-        <f>+HA26*(1+$AR$31)</f>
+        <f t="shared" si="83"/>
         <v>59623.507830010247</v>
       </c>
       <c r="HC26" s="1">
-        <f>+HB26*(1+$AR$31)</f>
+        <f t="shared" si="83"/>
         <v>60219.742908310349</v>
       </c>
       <c r="HD26" s="1">
-        <f>+HC26*(1+$AR$31)</f>
+        <f t="shared" si="83"/>
         <v>60821.940337393455</v>
       </c>
       <c r="HE26" s="1">
-        <f>+HD26*(1+$AR$31)</f>
+        <f t="shared" si="83"/>
         <v>61430.159740767391</v>
       </c>
       <c r="HF26" s="1">
-        <f>+HE26*(1+$AR$31)</f>
+        <f t="shared" si="83"/>
         <v>62044.461338175068</v>
       </c>
       <c r="HG26" s="1">
-        <f>+HF26*(1+$AR$31)</f>
+        <f t="shared" si="83"/>
         <v>62664.905951556822</v>
       </c>
       <c r="HH26" s="1">
-        <f>+HG26*(1+$AR$31)</f>
+        <f t="shared" si="83"/>
         <v>63291.555011072393</v>
       </c>
       <c r="HI26" s="1">
-        <f>+HH26*(1+$AR$31)</f>
+        <f t="shared" si="83"/>
         <v>63924.470561183116</v>
       </c>
       <c r="HJ26" s="1">
-        <f>+HI26*(1+$AR$31)</f>
+        <f t="shared" si="83"/>
         <v>64563.715266794949</v>
       </c>
       <c r="HK26" s="1">
-        <f>+HJ26*(1+$AR$31)</f>
+        <f t="shared" si="83"/>
         <v>65209.352419462899</v>
       </c>
       <c r="HL26" s="1">
-        <f>+HK26*(1+$AR$31)</f>
+        <f t="shared" si="83"/>
         <v>65861.445943657527</v>
       </c>
       <c r="HM26" s="1">
-        <f>+HL26*(1+$AR$31)</f>
+        <f t="shared" si="83"/>
         <v>66520.060403094103</v>
       </c>
       <c r="HN26" s="1">
-        <f>+HM26*(1+$AR$31)</f>
+        <f t="shared" si="83"/>
         <v>67185.261007125038</v>
       </c>
       <c r="HO26" s="1">
-        <f>+HN26*(1+$AR$31)</f>
+        <f t="shared" si="83"/>
         <v>67857.113617196286</v>
       </c>
       <c r="HP26" s="1">
-        <f>+HO26*(1+$AR$31)</f>
+        <f t="shared" si="83"/>
         <v>68535.684753368245</v>
       </c>
       <c r="HQ26" s="1">
-        <f>+HP26*(1+$AR$31)</f>
+        <f t="shared" si="83"/>
         <v>69221.041600901925</v>
       </c>
       <c r="HR26" s="1">
-        <f>+HQ26*(1+$AR$31)</f>
+        <f t="shared" si="83"/>
         <v>69913.252016910948</v>
       </c>
       <c r="HS26" s="1">
-        <f>+HR26*(1+$AR$31)</f>
+        <f t="shared" si="83"/>
         <v>70612.384537080055</v>
       </c>
       <c r="HT26" s="1">
-        <f>+HS26*(1+$AR$31)</f>
+        <f t="shared" si="83"/>
         <v>71318.508382450862</v>
       </c>
       <c r="HU26" s="1">
-        <f>+HT26*(1+$AR$31)</f>
+        <f t="shared" si="83"/>
         <v>72031.693466275377</v>
       </c>
       <c r="HV26" s="1">
-        <f>+HU26*(1+$AR$31)</f>
+        <f t="shared" si="83"/>
         <v>72752.010400938132</v>
       </c>
       <c r="HW26" s="1">
-        <f>+HV26*(1+$AR$31)</f>
+        <f t="shared" si="83"/>
         <v>73479.530504947514</v>
       </c>
       <c r="HX26" s="1">
-        <f>+HW26*(1+$AR$31)</f>
+        <f t="shared" si="83"/>
         <v>74214.325809996983</v>
       </c>
       <c r="HY26" s="1">
-        <f>+HX26*(1+$AR$31)</f>
+        <f t="shared" si="83"/>
         <v>74956.469068096951</v>
       </c>
       <c r="HZ26" s="1">
-        <f>+HY26*(1+$AR$31)</f>
+        <f t="shared" ref="HZ26:IG26" si="84">+HY26*(1+$AR$31)</f>
         <v>75706.033758777921</v>
       </c>
       <c r="IA26" s="1">
-        <f>+HZ26*(1+$AR$31)</f>
+        <f t="shared" si="84"/>
         <v>76463.094096365705</v>
       </c>
       <c r="IB26" s="1">
-        <f>+IA26*(1+$AR$31)</f>
+        <f t="shared" si="84"/>
         <v>77227.725037329365</v>
       </c>
       <c r="IC26" s="1">
-        <f>+IB26*(1+$AR$31)</f>
+        <f t="shared" si="84"/>
         <v>78000.002287702664</v>
       </c>
       <c r="ID26" s="1">
-        <f>+IC26*(1+$AR$31)</f>
+        <f t="shared" si="84"/>
         <v>78780.002310579686</v>
       </c>
       <c r="IE26" s="1">
-        <f>+ID26*(1+$AR$31)</f>
+        <f t="shared" si="84"/>
         <v>79567.802333685482</v>
       </c>
       <c r="IF26" s="1">
-        <f>+IE26*(1+$AR$31)</f>
+        <f t="shared" si="84"/>
         <v>80363.480357022345</v>
       </c>
       <c r="IG26" s="1">
-        <f>+IF26*(1+$AR$31)</f>
+        <f t="shared" si="84"/>
         <v>81167.11516059257</v>
       </c>
     </row>
@@ -5239,59 +5248,59 @@
         <v>33</v>
       </c>
       <c r="C30" s="21">
-        <f t="shared" ref="C30:M30" si="76">(C16-C17)/C16</f>
+        <f t="shared" ref="C30:M30" si="85">(C16-C17)/C16</f>
         <v>0.57265137905526786</v>
       </c>
       <c r="D30" s="21">
-        <f t="shared" si="76"/>
+        <f t="shared" si="85"/>
         <v>0.55223719676549865</v>
       </c>
       <c r="E30" s="21">
-        <f t="shared" si="76"/>
+        <f t="shared" si="85"/>
         <v>0.55129570465033728</v>
       </c>
       <c r="F30" s="21">
-        <f t="shared" si="76"/>
+        <f t="shared" si="85"/>
         <v>0.55045765264743363</v>
       </c>
       <c r="G30" s="21">
-        <f t="shared" si="76"/>
+        <f t="shared" si="85"/>
         <v>0.56597886260694519</v>
       </c>
       <c r="H30" s="21">
-        <f t="shared" si="76"/>
+        <f t="shared" si="85"/>
         <v>0.56267973160080942</v>
       </c>
       <c r="I30" s="21">
-        <f t="shared" si="76"/>
+        <f t="shared" si="85"/>
         <v>0.555626530394975</v>
       </c>
       <c r="J30" s="21">
-        <f t="shared" si="76"/>
+        <f t="shared" si="85"/>
         <v>0.56388482186432409</v>
       </c>
       <c r="K30" s="21">
-        <f t="shared" si="76"/>
+        <f t="shared" si="85"/>
         <v>0.55771702802296685</v>
       </c>
       <c r="L30" s="21">
-        <f t="shared" si="76"/>
+        <f t="shared" si="85"/>
         <v>0.55032334456690046</v>
       </c>
       <c r="M30" s="21">
-        <f t="shared" si="76"/>
+        <f t="shared" si="85"/>
         <v>0.5556198745779064</v>
       </c>
       <c r="N30" s="21">
-        <f t="shared" ref="N30" si="77">(N16-N17)/N16</f>
+        <f t="shared" ref="N30" si="86">(N16-N17)/N16</f>
         <v>0.55336704817673676</v>
       </c>
       <c r="O30" s="21">
-        <f t="shared" ref="O30:P30" si="78">(O16-O17)/O16</f>
+        <f t="shared" ref="O30:P30" si="87">(O16-O17)/O16</f>
         <v>0.54554358472086195</v>
       </c>
       <c r="P30" s="21">
-        <f t="shared" si="78"/>
+        <f t="shared" si="87"/>
         <v>1</v>
       </c>
       <c r="AB30" s="4">
@@ -5311,43 +5320,43 @@
         <v>0.55428597236022037</v>
       </c>
       <c r="AF30" s="4">
-        <f t="shared" ref="AF30:AN30" si="79">(AF16-AF17)/AF16</f>
+        <f t="shared" ref="AF30:AN30" si="88">(AF16-AF17)/AF16</f>
         <v>0.55428597236022037</v>
       </c>
       <c r="AG30" s="4">
-        <f t="shared" si="79"/>
+        <f t="shared" si="88"/>
         <v>0.55428597236022037</v>
       </c>
       <c r="AH30" s="4">
-        <f t="shared" si="79"/>
+        <f t="shared" si="88"/>
         <v>0.55428597236022037</v>
       </c>
       <c r="AI30" s="4">
-        <f t="shared" si="79"/>
+        <f t="shared" si="88"/>
         <v>0.55428597236022026</v>
       </c>
       <c r="AJ30" s="4">
-        <f t="shared" si="79"/>
+        <f t="shared" si="88"/>
         <v>0.55428597236022037</v>
       </c>
       <c r="AK30" s="4">
-        <f t="shared" si="79"/>
+        <f t="shared" si="88"/>
         <v>0.55428597236022037</v>
       </c>
       <c r="AL30" s="4">
-        <f t="shared" si="79"/>
+        <f t="shared" si="88"/>
         <v>0.55428597236022026</v>
       </c>
       <c r="AM30" s="4">
-        <f t="shared" si="79"/>
+        <f t="shared" si="88"/>
         <v>0.55428597236022026</v>
       </c>
       <c r="AN30" s="4">
-        <f t="shared" si="79"/>
+        <f t="shared" si="88"/>
         <v>0.55428597236022037</v>
       </c>
       <c r="AO30" s="4">
-        <f t="shared" ref="AO30" si="80">(AO16-AO17)/AO16</f>
+        <f t="shared" ref="AO30" si="89">(AO16-AO17)/AO16</f>
         <v>0.55428597236022037</v>
       </c>
       <c r="AQ30" s="1" t="s">
@@ -5362,43 +5371,43 @@
         <v>42</v>
       </c>
       <c r="C31" s="21">
-        <f t="shared" ref="C31" si="81">+C21/C16</f>
+        <f t="shared" ref="C31" si="90">+C21/C16</f>
         <v>0.26048821726725141</v>
       </c>
       <c r="D31" s="21">
-        <f t="shared" ref="D31" si="82">+D21/D16</f>
+        <f t="shared" ref="D31" si="91">+D21/D16</f>
         <v>0.22533692722371967</v>
       </c>
       <c r="E31" s="21">
-        <f t="shared" ref="E31:F31" si="83">+E21/E16</f>
+        <f t="shared" ref="E31:F31" si="92">+E21/E16</f>
         <v>0.21571411667258314</v>
       </c>
       <c r="F31" s="21">
-        <f t="shared" si="83"/>
+        <f t="shared" si="92"/>
         <v>0.16336461591936044</v>
       </c>
       <c r="G31" s="21">
-        <f t="shared" ref="G31:L31" si="84">+G21/G16</f>
+        <f t="shared" ref="G31:L31" si="93">+G21/G16</f>
         <v>0.29471565173628583</v>
       </c>
       <c r="H31" s="21">
-        <f t="shared" si="84"/>
+        <f t="shared" si="93"/>
         <v>0.24922781978911493</v>
       </c>
       <c r="I31" s="21">
-        <f t="shared" si="84"/>
+        <f t="shared" si="93"/>
         <v>0.23655913978494625</v>
       </c>
       <c r="J31" s="21">
-        <f t="shared" ref="J31" si="85">+J21/J16</f>
+        <f t="shared" ref="J31" si="94">+J21/J16</f>
         <v>0.25192776964372865</v>
       </c>
       <c r="K31" s="21">
-        <f t="shared" si="84"/>
+        <f t="shared" si="93"/>
         <v>0.30465335504327706</v>
       </c>
       <c r="L31" s="21">
-        <f t="shared" si="84"/>
+        <f t="shared" si="93"/>
         <v>0.28417888696602606</v>
       </c>
       <c r="M31" s="21">
@@ -5414,7 +5423,7 @@
         <v>0.27473065621939274</v>
       </c>
       <c r="P31" s="21">
-        <f t="shared" ref="P31" si="86">+P21/P16</f>
+        <f t="shared" ref="P31" si="95">+P21/P16</f>
         <v>0</v>
       </c>
       <c r="AB31" s="4">
@@ -5434,43 +5443,43 @@
         <v>0.27899467076144885</v>
       </c>
       <c r="AF31" s="4">
-        <f t="shared" ref="AF31:AN31" si="87">+AF21/AF16</f>
+        <f t="shared" ref="AF31:AN31" si="96">+AF21/AF16</f>
         <v>0.27899467076144885</v>
       </c>
       <c r="AG31" s="4">
-        <f t="shared" si="87"/>
+        <f t="shared" si="96"/>
         <v>0.27899467076144874</v>
       </c>
       <c r="AH31" s="4">
-        <f t="shared" si="87"/>
+        <f t="shared" si="96"/>
         <v>0.27899467076144879</v>
       </c>
       <c r="AI31" s="4">
-        <f t="shared" si="87"/>
+        <f t="shared" si="96"/>
         <v>0.27899467076144868</v>
       </c>
       <c r="AJ31" s="4">
-        <f t="shared" si="87"/>
+        <f t="shared" si="96"/>
         <v>0.27899467076144879</v>
       </c>
       <c r="AK31" s="4">
-        <f t="shared" si="87"/>
+        <f t="shared" si="96"/>
         <v>0.27899467076144863</v>
       </c>
       <c r="AL31" s="4">
-        <f t="shared" si="87"/>
+        <f t="shared" si="96"/>
         <v>0.2789946707614489</v>
       </c>
       <c r="AM31" s="4">
-        <f t="shared" si="87"/>
+        <f t="shared" si="96"/>
         <v>0.27899467076144879</v>
       </c>
       <c r="AN31" s="4">
-        <f t="shared" si="87"/>
+        <f t="shared" si="96"/>
         <v>0.27899467076144874</v>
       </c>
       <c r="AO31" s="4">
-        <f t="shared" ref="AO31" si="88">+AO21/AO16</f>
+        <f t="shared" ref="AO31" si="97">+AO21/AO16</f>
         <v>0.27899467076144874</v>
       </c>
       <c r="AQ31" s="1" t="s">
@@ -5542,35 +5551,35 @@
         <v>0.2159437500000001</v>
       </c>
       <c r="AH33" s="4">
-        <f t="shared" ref="AH33:AO33" si="89">+AH3/AG3-1</f>
+        <f t="shared" ref="AH33:AO33" si="98">+AH3/AG3-1</f>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="AI33" s="4">
-        <f t="shared" si="89"/>
+        <f t="shared" si="98"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="AJ33" s="4">
-        <f t="shared" si="89"/>
+        <f t="shared" si="98"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="AK33" s="4">
-        <f t="shared" si="89"/>
+        <f t="shared" si="98"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="AL33" s="4">
-        <f t="shared" si="89"/>
+        <f t="shared" si="98"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="AM33" s="4">
-        <f t="shared" si="89"/>
+        <f t="shared" si="98"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="AN33" s="4">
-        <f t="shared" si="89"/>
+        <f t="shared" si="98"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="AO33" s="4">
-        <f t="shared" si="89"/>
+        <f t="shared" si="98"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="AQ33" s="6" t="s">
@@ -5598,55 +5607,55 @@
       <c r="M34" s="21"/>
       <c r="N34" s="21"/>
       <c r="O34" s="21">
-        <f t="shared" ref="O34:P41" si="90">+O4/K4-1</f>
+        <f t="shared" ref="O34:P41" si="99">+O4/K4-1</f>
         <v>0.14568158168574397</v>
       </c>
       <c r="P34" s="21">
-        <f t="shared" si="90"/>
+        <f t="shared" si="99"/>
         <v>0.3600000000000001</v>
       </c>
       <c r="AE34" s="4">
-        <f t="shared" ref="AE34:AF41" si="91">+AE4/AD4-1</f>
+        <f t="shared" ref="AE34:AF41" si="100">+AE4/AD4-1</f>
         <v>0.35979381443298974</v>
       </c>
       <c r="AF34" s="4">
-        <f t="shared" si="91"/>
+        <f t="shared" si="100"/>
         <v>0.31841293909527413</v>
       </c>
       <c r="AG34" s="4">
-        <f t="shared" ref="AG34:AO34" si="92">+AG4/AF4-1</f>
+        <f t="shared" ref="AG34:AO34" si="101">+AG4/AF4-1</f>
         <v>0.30000000000000004</v>
       </c>
       <c r="AH34" s="4">
-        <f t="shared" si="92"/>
+        <f t="shared" si="101"/>
         <v>0.25</v>
       </c>
       <c r="AI34" s="4">
-        <f t="shared" si="92"/>
+        <f t="shared" si="101"/>
         <v>0.19999999999999996</v>
       </c>
       <c r="AJ34" s="4">
-        <f t="shared" si="92"/>
+        <f t="shared" si="101"/>
         <v>0.14999999999999991</v>
       </c>
       <c r="AK34" s="4">
-        <f t="shared" si="92"/>
+        <f t="shared" si="101"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="AL34" s="4">
-        <f t="shared" si="92"/>
+        <f t="shared" si="101"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="AM34" s="4">
-        <f t="shared" si="92"/>
+        <f t="shared" si="101"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="AN34" s="4">
-        <f t="shared" si="92"/>
+        <f t="shared" si="101"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="AO34" s="4">
-        <f t="shared" si="92"/>
+        <f t="shared" si="101"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="AQ34" s="1" t="s">
@@ -5674,55 +5683,55 @@
       <c r="M35" s="21"/>
       <c r="N35" s="21"/>
       <c r="O35" s="21">
-        <f t="shared" si="90"/>
+        <f t="shared" si="99"/>
         <v>8.9735313105229197E-2</v>
       </c>
       <c r="P35" s="21">
-        <f t="shared" si="90"/>
+        <f t="shared" si="99"/>
         <v>0.12999999999999989</v>
       </c>
       <c r="AE35" s="4">
-        <f t="shared" si="91"/>
+        <f t="shared" si="100"/>
         <v>0.22017333579199705</v>
       </c>
       <c r="AF35" s="4">
-        <f t="shared" si="91"/>
+        <f t="shared" si="100"/>
         <v>7.9963729786912241E-2</v>
       </c>
       <c r="AG35" s="4">
-        <f t="shared" ref="AG35:AO35" si="93">+AG5/AF5-1</f>
+        <f t="shared" ref="AG35:AO35" si="102">+AG5/AF5-1</f>
         <v>8.0000000000000071E-2</v>
       </c>
       <c r="AH35" s="4">
-        <f t="shared" si="93"/>
+        <f t="shared" si="102"/>
         <v>8.0000000000000071E-2</v>
       </c>
       <c r="AI35" s="4">
-        <f t="shared" si="93"/>
+        <f t="shared" si="102"/>
         <v>8.0000000000000071E-2</v>
       </c>
       <c r="AJ35" s="4">
-        <f t="shared" si="93"/>
+        <f t="shared" si="102"/>
         <v>8.0000000000000071E-2</v>
       </c>
       <c r="AK35" s="4">
-        <f t="shared" si="93"/>
+        <f t="shared" si="102"/>
         <v>8.0000000000000071E-2</v>
       </c>
       <c r="AL35" s="4">
-        <f t="shared" si="93"/>
+        <f t="shared" si="102"/>
         <v>8.0000000000000071E-2</v>
       </c>
       <c r="AM35" s="4">
-        <f t="shared" si="93"/>
+        <f t="shared" si="102"/>
         <v>8.0000000000000071E-2</v>
       </c>
       <c r="AN35" s="4">
-        <f t="shared" si="93"/>
+        <f t="shared" si="102"/>
         <v>8.0000000000000071E-2</v>
       </c>
       <c r="AO35" s="4">
-        <f t="shared" si="93"/>
+        <f t="shared" si="102"/>
         <v>8.0000000000000071E-2</v>
       </c>
       <c r="AQ35" s="6" t="s">
@@ -5750,55 +5759,55 @@
       <c r="M36" s="21"/>
       <c r="N36" s="21"/>
       <c r="O36" s="21">
-        <f t="shared" si="90"/>
+        <f t="shared" si="99"/>
         <v>5.2459341531138515E-2</v>
       </c>
       <c r="P36" s="21">
-        <f t="shared" si="90"/>
+        <f t="shared" si="99"/>
         <v>-3.9944027880451927E-2</v>
       </c>
       <c r="AE36" s="4">
-        <f t="shared" si="91"/>
+        <f t="shared" si="100"/>
         <v>0.15577177973249778</v>
       </c>
       <c r="AF36" s="4">
-        <f t="shared" si="91"/>
+        <f t="shared" si="100"/>
         <v>-5.2230302082518776E-2</v>
       </c>
       <c r="AG36" s="4">
-        <f t="shared" ref="AG36:AO38" si="94">+AG6/AF6-1</f>
+        <f t="shared" ref="AG36:AO38" si="103">+AG6/AF6-1</f>
         <v>0.20128733869628213</v>
       </c>
       <c r="AH36" s="4">
-        <f t="shared" si="94"/>
+        <f t="shared" si="103"/>
         <v>8.6351939832318481E-2</v>
       </c>
       <c r="AI36" s="4">
-        <f t="shared" si="94"/>
+        <f t="shared" si="103"/>
         <v>8.2066264867828531E-2</v>
       </c>
       <c r="AJ36" s="4">
-        <f t="shared" si="94"/>
+        <f t="shared" si="103"/>
         <v>7.5070962924173035E-2</v>
       </c>
       <c r="AK36" s="4">
-        <f t="shared" si="94"/>
+        <f t="shared" si="103"/>
         <v>6.5879666198442877E-2</v>
       </c>
       <c r="AL36" s="4">
-        <f t="shared" si="94"/>
+        <f t="shared" si="103"/>
         <v>6.6288859237014774E-2</v>
       </c>
       <c r="AM36" s="4">
-        <f t="shared" si="94"/>
+        <f t="shared" si="103"/>
         <v>6.6703425319999399E-2</v>
       </c>
       <c r="AN36" s="4">
-        <f t="shared" si="94"/>
+        <f t="shared" si="103"/>
         <v>6.7123149524337844E-2</v>
       </c>
       <c r="AO36" s="4">
-        <f t="shared" si="94"/>
+        <f t="shared" si="103"/>
         <v>6.7547803265934458E-2</v>
       </c>
       <c r="AQ36" s="1" t="s">
@@ -5826,51 +5835,51 @@
       <c r="M37" s="21"/>
       <c r="N37" s="21"/>
       <c r="O37" s="21">
-        <f t="shared" si="90"/>
+        <f t="shared" si="99"/>
         <v>3.7133550488599454E-2</v>
       </c>
       <c r="P37" s="21">
-        <f t="shared" si="90"/>
+        <f t="shared" si="99"/>
         <v>-1.4404852160727843E-2</v>
       </c>
       <c r="AE37" s="4">
-        <f t="shared" si="91"/>
+        <f t="shared" si="100"/>
         <v>1.7946877243359971E-3</v>
       </c>
       <c r="AG37" s="4">
-        <f t="shared" si="94"/>
+        <f t="shared" si="103"/>
         <v>0.12713461538461535</v>
       </c>
       <c r="AH37" s="4">
-        <f t="shared" si="94"/>
+        <f t="shared" si="103"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="AI37" s="4">
-        <f t="shared" si="94"/>
+        <f t="shared" si="103"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="AJ37" s="4">
-        <f t="shared" si="94"/>
+        <f t="shared" si="103"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="AK37" s="4">
-        <f t="shared" si="94"/>
+        <f t="shared" si="103"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="AL37" s="4">
-        <f t="shared" si="94"/>
+        <f t="shared" si="103"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="AM37" s="4">
-        <f t="shared" si="94"/>
+        <f t="shared" si="103"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="AN37" s="4">
-        <f t="shared" si="94"/>
+        <f t="shared" si="103"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="AO37" s="4">
-        <f t="shared" si="94"/>
+        <f t="shared" si="103"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="AQ37" s="1" t="s">
@@ -5898,51 +5907,51 @@
       <c r="M38" s="21"/>
       <c r="N38" s="21"/>
       <c r="O38" s="21">
-        <f t="shared" si="90"/>
+        <f t="shared" si="99"/>
         <v>3.7133550488599454E-2</v>
       </c>
       <c r="P38" s="21">
-        <f t="shared" si="90"/>
+        <f t="shared" si="99"/>
         <v>-1.4404852160727843E-2</v>
       </c>
       <c r="AE38" s="4">
-        <f t="shared" si="91"/>
+        <f t="shared" si="100"/>
         <v>1.7946877243359971E-3</v>
       </c>
       <c r="AG38" s="4">
-        <f t="shared" si="94"/>
+        <f t="shared" si="103"/>
         <v>0.12713461538461535</v>
       </c>
       <c r="AH38" s="4">
-        <f t="shared" si="94"/>
+        <f t="shared" si="103"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="AI38" s="4">
-        <f t="shared" si="94"/>
+        <f t="shared" si="103"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="AJ38" s="4">
-        <f t="shared" si="94"/>
+        <f t="shared" si="103"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="AK38" s="4">
-        <f t="shared" si="94"/>
+        <f t="shared" si="103"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="AL38" s="4">
-        <f t="shared" si="94"/>
+        <f t="shared" si="103"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="AM38" s="4">
-        <f t="shared" si="94"/>
+        <f t="shared" si="103"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="AN38" s="4">
-        <f t="shared" si="94"/>
+        <f t="shared" si="103"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="AO38" s="4">
-        <f t="shared" si="94"/>
+        <f t="shared" si="103"/>
         <v>0.10000000000000009</v>
       </c>
     </row>
@@ -5965,7 +5974,7 @@
       <c r="O39" s="21"/>
       <c r="P39" s="21"/>
       <c r="AE39" s="4">
-        <f t="shared" si="91"/>
+        <f t="shared" si="100"/>
         <v>-1</v>
       </c>
     </row>
@@ -5988,7 +5997,7 @@
       <c r="O40" s="21"/>
       <c r="P40" s="21"/>
       <c r="AE40" s="4">
-        <f t="shared" si="91"/>
+        <f t="shared" si="100"/>
         <v>-1</v>
       </c>
     </row>
@@ -6009,15 +6018,15 @@
       <c r="M41" s="21"/>
       <c r="N41" s="21"/>
       <c r="O41" s="21">
-        <f t="shared" si="90"/>
+        <f t="shared" si="99"/>
         <v>5.0434632928823442E-2</v>
       </c>
       <c r="P41" s="21">
-        <f t="shared" si="90"/>
+        <f t="shared" si="99"/>
         <v>-3.682146829810895E-2</v>
       </c>
       <c r="AE41" s="4">
-        <f t="shared" si="91"/>
+        <f t="shared" si="100"/>
         <v>0.13311504150982323</v>
       </c>
     </row>
@@ -6078,48 +6087,48 @@
       <c r="E45" s="21"/>
       <c r="F45" s="21"/>
       <c r="G45" s="21">
-        <f>+G14/C14-1</f>
+        <f t="shared" ref="G45:O47" si="104">+G14/C14-1</f>
         <v>6.8345323741007213E-2</v>
       </c>
       <c r="H45" s="21">
-        <f>+H14/D14-1</f>
+        <f t="shared" si="104"/>
         <v>1.3255161865918907E-2</v>
       </c>
       <c r="I45" s="21">
-        <f>+I14/E14-1</f>
+        <f t="shared" si="104"/>
         <v>0.12450759707371972</v>
       </c>
       <c r="J45" s="21">
-        <f>+J14/F14-1</f>
+        <f t="shared" si="104"/>
         <v>0.17037037037037028</v>
       </c>
       <c r="K45" s="21">
-        <f>+K14/G14-1</f>
+        <f t="shared" si="104"/>
         <v>0.19552669552669544</v>
       </c>
       <c r="L45" s="21">
-        <f>+L14/H14-1</f>
+        <f t="shared" si="104"/>
         <v>0.17723270440251571</v>
       </c>
       <c r="M45" s="21">
-        <f>+M14/I14-1</f>
+        <f t="shared" si="104"/>
         <v>0.11259852370824475</v>
       </c>
       <c r="N45" s="21">
-        <f>+N14/J14-1</f>
+        <f t="shared" si="104"/>
         <v>0.13396624472573837</v>
       </c>
       <c r="O45" s="21">
-        <f>+O14/K14-1</f>
+        <f t="shared" si="104"/>
         <v>5.2705693019513111E-2</v>
       </c>
       <c r="P45" s="21"/>
       <c r="AC45" s="4">
-        <f>+AC14/AB14-1</f>
+        <f t="shared" ref="AC45:AD47" si="105">+AC14/AB14-1</f>
         <v>-0.1921659358101746</v>
       </c>
       <c r="AD45" s="4">
-        <f>+AD14/AC14-1</f>
+        <f t="shared" si="105"/>
         <v>9.2014120154522372E-2</v>
       </c>
     </row>
@@ -6132,48 +6141,48 @@
       <c r="E46" s="21"/>
       <c r="F46" s="21"/>
       <c r="G46" s="21">
-        <f>+G15/C15-1</f>
+        <f t="shared" si="104"/>
         <v>-3.5735556879094688E-2</v>
       </c>
       <c r="H46" s="21">
-        <f>+H15/D15-1</f>
+        <f t="shared" si="104"/>
         <v>6.9979006298110935E-3</v>
       </c>
       <c r="I46" s="21">
-        <f>+I15/E15-1</f>
+        <f t="shared" si="104"/>
         <v>4.2442293373045503E-2</v>
       </c>
       <c r="J46" s="21">
-        <f>+J15/F15-1</f>
+        <f t="shared" si="104"/>
         <v>0.27740492170022368</v>
       </c>
       <c r="K46" s="21">
-        <f>+K15/G15-1</f>
+        <f t="shared" si="104"/>
         <v>6.6707844348363077E-2</v>
       </c>
       <c r="L46" s="21">
-        <f>+L15/H15-1</f>
+        <f t="shared" si="104"/>
         <v>0.12578179291174418</v>
       </c>
       <c r="M46" s="21">
-        <f>+M15/I15-1</f>
+        <f t="shared" si="104"/>
         <v>5.1428571428571379E-2</v>
       </c>
       <c r="N46" s="21">
-        <f>+N15/J15-1</f>
+        <f t="shared" si="104"/>
         <v>-6.8301225919439545E-2</v>
       </c>
       <c r="O46" s="21">
-        <f>+O15/K15-1</f>
+        <f t="shared" si="104"/>
         <v>3.4163288940358916E-2</v>
       </c>
       <c r="P46" s="21"/>
       <c r="AC46" s="4">
-        <f>+AC15/AB15-1</f>
+        <f t="shared" si="105"/>
         <v>-0.17598520415421826</v>
       </c>
       <c r="AD46" s="4">
-        <f>+AD15/AC15-1</f>
+        <f t="shared" si="105"/>
         <v>6.5435082872928207E-2</v>
       </c>
     </row>
@@ -6186,39 +6195,39 @@
       <c r="E47" s="23"/>
       <c r="F47" s="23"/>
       <c r="G47" s="23">
-        <f>+G16/C16-1</f>
+        <f t="shared" si="104"/>
         <v>4.9878474056852973E-2</v>
       </c>
       <c r="H47" s="23">
-        <f>+H16/D16-1</f>
+        <f t="shared" si="104"/>
         <v>1.2291105121293722E-2</v>
       </c>
       <c r="I47" s="23">
-        <f>+I16/E16-1</f>
+        <f t="shared" si="104"/>
         <v>0.11146609868654589</v>
       </c>
       <c r="J47" s="23">
-        <f>+J16/F16-1</f>
+        <f t="shared" si="104"/>
         <v>0.18700034758428918</v>
       </c>
       <c r="K47" s="23">
-        <f>+K16/G16-1</f>
+        <f t="shared" si="104"/>
         <v>0.17453447408153</v>
       </c>
       <c r="L47" s="23">
-        <f>+L16/H16-1</f>
+        <f t="shared" si="104"/>
         <v>0.16934710831824473</v>
       </c>
       <c r="M47" s="23">
-        <f>+M16/I16-1</f>
+        <f t="shared" si="104"/>
         <v>0.10348131587352283</v>
       </c>
       <c r="N47" s="23">
-        <f>+N16/J16-1</f>
+        <f t="shared" si="104"/>
         <v>0.1001464128843339</v>
       </c>
       <c r="O47" s="23">
-        <f>+O16/K16-1</f>
+        <f t="shared" si="104"/>
         <v>4.9961436284171823E-2</v>
       </c>
       <c r="P47" s="23">
@@ -6226,11 +6235,11 @@
         <v>-3.4520448128244841E-2</v>
       </c>
       <c r="AC47" s="7">
-        <f>+AC16/AB16-1</f>
+        <f t="shared" si="105"/>
         <v>-0.18959276018099547</v>
       </c>
       <c r="AD47" s="7">
-        <f>+AD16/AC16-1</f>
+        <f t="shared" si="105"/>
         <v>8.7716359575656044E-2</v>
       </c>
       <c r="AE47" s="7">
@@ -6238,43 +6247,43 @@
         <v>0.13659463066577682</v>
       </c>
       <c r="AF47" s="7">
-        <f t="shared" ref="AF47:AO47" si="95">+AF16/AE16-1</f>
+        <f t="shared" ref="AF47:AO47" si="106">+AF16/AE16-1</f>
         <v>-4.2543582332219332E-2</v>
       </c>
       <c r="AG47" s="7">
-        <f t="shared" si="95"/>
+        <f t="shared" si="106"/>
         <v>0.16848131132075483</v>
       </c>
       <c r="AH47" s="7">
-        <f t="shared" si="95"/>
+        <f t="shared" si="106"/>
         <v>8.7966530479302252E-2</v>
       </c>
       <c r="AI47" s="7">
-        <f t="shared" si="95"/>
+        <f t="shared" si="106"/>
         <v>8.4211324673816756E-2</v>
       </c>
       <c r="AJ47" s="7">
-        <f t="shared" si="95"/>
+        <f t="shared" si="106"/>
         <v>7.8096154646271954E-2</v>
       </c>
       <c r="AK47" s="7">
-        <f t="shared" si="95"/>
+        <f t="shared" si="106"/>
         <v>7.0104366048096445E-2</v>
       </c>
       <c r="AL47" s="7">
-        <f t="shared" si="95"/>
+        <f t="shared" si="106"/>
         <v>7.0579504265524395E-2</v>
       </c>
       <c r="AM47" s="7">
-        <f t="shared" si="95"/>
+        <f t="shared" si="106"/>
         <v>7.1057766514359022E-2</v>
       </c>
       <c r="AN47" s="7">
-        <f t="shared" si="95"/>
+        <f t="shared" si="106"/>
         <v>7.1538781752707781E-2</v>
       </c>
       <c r="AO47" s="7">
-        <f t="shared" si="95"/>
+        <f t="shared" si="106"/>
         <v>7.2022170019822918E-2</v>
       </c>
     </row>
@@ -6303,43 +6312,43 @@
         <v>-2404.92</v>
       </c>
       <c r="AF50" s="1">
-        <f t="shared" ref="AF50:AO50" si="96">+AE50*0.95</f>
+        <f t="shared" ref="AF50:AO50" si="107">+AE50*0.95</f>
         <v>-2284.674</v>
       </c>
       <c r="AG50" s="1">
-        <f t="shared" si="96"/>
+        <f t="shared" si="107"/>
         <v>-2170.4402999999998</v>
       </c>
       <c r="AH50" s="1">
-        <f t="shared" si="96"/>
+        <f t="shared" si="107"/>
         <v>-2061.9182849999997</v>
       </c>
       <c r="AI50" s="1">
-        <f t="shared" si="96"/>
+        <f t="shared" si="107"/>
         <v>-1958.8223707499997</v>
       </c>
       <c r="AJ50" s="1">
-        <f t="shared" si="96"/>
+        <f t="shared" si="107"/>
         <v>-1860.8812522124997</v>
       </c>
       <c r="AK50" s="1">
-        <f t="shared" si="96"/>
+        <f t="shared" si="107"/>
         <v>-1767.8371896018746</v>
       </c>
       <c r="AL50" s="1">
-        <f t="shared" si="96"/>
+        <f t="shared" si="107"/>
         <v>-1679.4453301217807</v>
       </c>
       <c r="AM50" s="1">
-        <f t="shared" si="96"/>
+        <f t="shared" si="107"/>
         <v>-1595.4730636156917</v>
       </c>
       <c r="AN50" s="1">
-        <f t="shared" si="96"/>
+        <f t="shared" si="107"/>
         <v>-1515.6994104349071</v>
       </c>
       <c r="AO50" s="1">
-        <f t="shared" si="96"/>
+        <f t="shared" si="107"/>
         <v>-1439.9144399131617</v>
       </c>
     </row>
@@ -6528,7 +6537,7 @@
         <v>2709</v>
       </c>
     </row>
-    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B65" s="1" t="s">
         <v>63</v>
       </c>
@@ -6542,7 +6551,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B66" s="1" t="s">
         <v>64</v>
       </c>
@@ -6556,7 +6565,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B67" s="1" t="s">
         <v>65</v>
       </c>
@@ -6570,7 +6579,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B68" s="1" t="s">
         <v>66</v>
       </c>
@@ -6584,7 +6593,7 @@
         <v>5229</v>
       </c>
     </row>
-    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B69" s="1" t="s">
         <v>64</v>
       </c>
@@ -6598,7 +6607,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B70" s="1" t="s">
         <v>67</v>
       </c>
@@ -6612,7 +6621,7 @@
         <v>14817</v>
       </c>
     </row>
-    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B71" s="1" t="s">
         <v>68</v>
       </c>
@@ -6626,7 +6635,7 @@
         <v>5243</v>
       </c>
     </row>
-    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B72" s="1" t="s">
         <v>69</v>
       </c>
@@ -6643,7 +6652,7 @@
         <v>29961</v>
       </c>
     </row>
-    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B73" s="1" t="s">
         <v>70</v>
       </c>
@@ -6657,7 +6666,7 @@
         <v>23073</v>
       </c>
     </row>
-    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B74" s="1" t="s">
         <v>71</v>
       </c>
@@ -6674,239 +6683,304 @@
         <v>53034</v>
       </c>
     </row>
-    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B76" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="M76" s="10">
+        <f t="shared" ref="M76:N76" si="108">(M54/SUM(J17:M17)*365)</f>
+        <v>64.920196119340716</v>
+      </c>
+      <c r="N76" s="10">
+        <f t="shared" si="108"/>
+        <v>79.794052082277844</v>
+      </c>
+      <c r="O76" s="10">
+        <f>(O54/SUM(L17:O17)*365)</f>
+        <v>75.246711342764954</v>
+      </c>
+    </row>
+    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B77" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="M77" s="10">
+        <f t="shared" ref="M77:N77" si="109">(M55/SUM(J17:M17)*365)</f>
+        <v>120.66398915084497</v>
+      </c>
+      <c r="N77" s="10">
+        <f t="shared" si="109"/>
+        <v>120.68041341574629</v>
+      </c>
+      <c r="O77" s="10">
+        <f>(O55/SUM(L17:O17)*365)</f>
+        <v>120.76073467361628</v>
+      </c>
+    </row>
+    <row r="78" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B78" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="M78" s="10">
+        <f t="shared" ref="M78:N78" si="110">(M64/SUM(J17:M17)*365)</f>
+        <v>44.492228249530562</v>
+      </c>
+      <c r="N78" s="10">
+        <f t="shared" si="110"/>
+        <v>51.611865437227685</v>
+      </c>
+      <c r="O78" s="10">
+        <f>(O64/SUM(L17:O17)*365)</f>
+        <v>49.083395383469849</v>
+      </c>
+    </row>
+    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="M79" s="10">
+        <f>+SUM(M76:M77)-M78</f>
+        <v>141.09195702065512</v>
+      </c>
+      <c r="N79" s="10">
+        <f>+SUM(N76:N77)-N78</f>
+        <v>148.86260006079644</v>
+      </c>
+      <c r="O79" s="10">
+        <f>+SUM(O76:O77)-O78</f>
+        <v>146.92405063291139</v>
+      </c>
+    </row>
+    <row r="83" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="B83" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="G77" s="10">
+      <c r="G83" s="10">
         <v>2949</v>
       </c>
-      <c r="H77" s="10">
-        <f>6503-G77</f>
+      <c r="H83" s="10">
+        <f>6503-G83</f>
         <v>3554</v>
       </c>
-      <c r="I77" s="10">
-        <f>9555-H77-G77</f>
+      <c r="I83" s="10">
+        <f>9555-H83-G83</f>
         <v>3052</v>
       </c>
-      <c r="J77" s="10">
-        <f>+AD77-SUM(G77:I77)</f>
+      <c r="J83" s="10">
+        <f>+AD83-SUM(G83:I83)</f>
         <v>2647</v>
       </c>
-      <c r="K77" s="10">
+      <c r="K83" s="10">
         <v>4587</v>
       </c>
-      <c r="L77" s="10">
-        <f>7141-K77</f>
+      <c r="L83" s="10">
+        <f>7141-K83</f>
         <v>2554</v>
       </c>
-      <c r="M77" s="10">
-        <f>10016-L77-K77</f>
+      <c r="M83" s="10">
+        <f>10016-L83-K83</f>
         <v>2875</v>
       </c>
-      <c r="N77" s="10">
-        <f>+AE77-SUM(K77:M77)</f>
+      <c r="N83" s="10">
+        <f>+AE83-SUM(K83:M83)</f>
         <v>3996</v>
       </c>
-      <c r="O77" s="10">
+      <c r="O83" s="10">
         <v>4965</v>
       </c>
-      <c r="AD77" s="1">
+      <c r="AD83" s="1">
         <v>12202</v>
       </c>
-      <c r="AE77" s="1">
+      <c r="AE83" s="1">
         <v>14012</v>
       </c>
     </row>
-    <row r="78" spans="2:31" x14ac:dyDescent="0.2">
-      <c r="B78" s="1" t="s">
+    <row r="84" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="B84" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="G78" s="10">
+      <c r="G84" s="10">
         <v>-214</v>
       </c>
-      <c r="H78" s="10">
-        <f>+-398-G78</f>
+      <c r="H84" s="10">
+        <f>+-398-G84</f>
         <v>-184</v>
       </c>
-      <c r="I78" s="10">
-        <f>+-785-H78-G78</f>
+      <c r="I84" s="10">
+        <f>+-785-H84-G84</f>
         <v>-387</v>
       </c>
-      <c r="J78" s="10">
-        <f>+AD78-SUM(G78:I78)</f>
+      <c r="J84" s="10">
+        <f>+AD84-SUM(G84:I84)</f>
         <v>-256</v>
       </c>
-      <c r="K78" s="10">
+      <c r="K84" s="10">
         <v>-277</v>
       </c>
-      <c r="L78" s="10">
-        <f>+-491-K78</f>
+      <c r="L84" s="10">
+        <f>+-491-K84</f>
         <v>-214</v>
       </c>
-      <c r="M78" s="10">
-        <f>+-785-L78-K78</f>
+      <c r="M84" s="10">
+        <f>+-785-L84-K84</f>
         <v>-294</v>
       </c>
-      <c r="N78" s="10">
-        <f>+AE78-SUM(K78:M78)</f>
+      <c r="N84" s="10">
+        <f>+AE84-SUM(K84:M84)</f>
         <v>-407</v>
       </c>
-      <c r="O78" s="10">
+      <c r="O84" s="10">
         <v>-549</v>
       </c>
-      <c r="AD78" s="1">
+      <c r="AD84" s="1">
         <v>-1041</v>
       </c>
-      <c r="AE78" s="1">
+      <c r="AE84" s="1">
         <v>-1192</v>
       </c>
     </row>
-    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
-      <c r="B79" s="1" t="s">
+    <row r="85" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="B85" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="G79" s="10">
-        <f>+G77+G78</f>
+      <c r="G85" s="10">
+        <f t="shared" ref="G85:O85" si="111">+G83+G84</f>
         <v>2735</v>
       </c>
-      <c r="H79" s="10">
-        <f>+H77+H78</f>
+      <c r="H85" s="10">
+        <f t="shared" si="111"/>
         <v>3370</v>
       </c>
-      <c r="I79" s="10">
-        <f>+I77+I78</f>
+      <c r="I85" s="10">
+        <f t="shared" si="111"/>
         <v>2665</v>
       </c>
-      <c r="J79" s="10">
-        <f>+J77+J78</f>
+      <c r="J85" s="10">
+        <f t="shared" si="111"/>
         <v>2391</v>
       </c>
-      <c r="K79" s="10">
-        <f>+K77+K78</f>
+      <c r="K85" s="10">
+        <f t="shared" si="111"/>
         <v>4310</v>
       </c>
-      <c r="L79" s="10">
-        <f>+L77+L78</f>
+      <c r="L85" s="10">
+        <f t="shared" si="111"/>
         <v>2340</v>
       </c>
-      <c r="M79" s="10">
-        <f>+M77+M78</f>
+      <c r="M85" s="10">
+        <f t="shared" si="111"/>
         <v>2581</v>
       </c>
-      <c r="N79" s="10">
-        <f>+N77+N78</f>
+      <c r="N85" s="10">
+        <f t="shared" si="111"/>
         <v>3589</v>
       </c>
-      <c r="O79" s="10">
-        <f>+O77+O78</f>
+      <c r="O85" s="10">
+        <f t="shared" si="111"/>
         <v>4416</v>
       </c>
-      <c r="AD79" s="10">
-        <f>+AD77+AD78</f>
+      <c r="AD85" s="10">
+        <f>+AD83+AD84</f>
         <v>11161</v>
       </c>
-      <c r="AE79" s="10">
-        <f>+AE77+AE78</f>
+      <c r="AE85" s="10">
+        <f>+AE83+AE84</f>
         <v>12820</v>
       </c>
     </row>
-    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
-      <c r="B80" s="1" t="s">
+    <row r="86" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="B86" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="G80" s="10">
+      <c r="G86" s="10">
         <f>+G26</f>
         <v>2811</v>
       </c>
-      <c r="H80" s="10">
-        <f t="shared" ref="H80:O80" si="97">+H26</f>
+      <c r="H86" s="10">
+        <f t="shared" ref="H86:O86" si="112">+H26</f>
         <v>2275</v>
       </c>
-      <c r="I80" s="10">
-        <f t="shared" si="97"/>
+      <c r="I86" s="10">
+        <f t="shared" si="112"/>
         <v>2109</v>
       </c>
-      <c r="J80" s="10">
-        <f t="shared" si="97"/>
+      <c r="J86" s="10">
+        <f t="shared" si="112"/>
         <v>2915</v>
       </c>
-      <c r="K80" s="10">
-        <f t="shared" si="97"/>
+      <c r="K86" s="10">
+        <f t="shared" si="112"/>
         <v>3180</v>
       </c>
-      <c r="L80" s="10">
-        <f t="shared" si="97"/>
+      <c r="L86" s="10">
+        <f t="shared" si="112"/>
         <v>2812</v>
       </c>
-      <c r="M80" s="10">
-        <f t="shared" si="97"/>
+      <c r="M86" s="10">
+        <f t="shared" si="112"/>
         <v>2666</v>
       </c>
-      <c r="N80" s="10">
-        <f t="shared" si="97"/>
+      <c r="N86" s="10">
+        <f t="shared" si="112"/>
         <v>-3117</v>
       </c>
-      <c r="O80" s="10">
-        <f t="shared" si="97"/>
+      <c r="O86" s="10">
+        <f t="shared" si="112"/>
         <v>3004</v>
       </c>
     </row>
-    <row r="82" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B82" s="1" t="s">
+    <row r="88" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="B88" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="J82" s="10">
-        <f t="shared" ref="J82:N82" si="98">SUM(G79:J79)</f>
+      <c r="J88" s="10">
+        <f t="shared" ref="J88:N88" si="113">SUM(G85:J85)</f>
         <v>11161</v>
       </c>
-      <c r="K82" s="10">
-        <f t="shared" si="98"/>
+      <c r="K88" s="10">
+        <f t="shared" si="113"/>
         <v>12736</v>
       </c>
-      <c r="L82" s="10">
-        <f t="shared" si="98"/>
+      <c r="L88" s="10">
+        <f t="shared" si="113"/>
         <v>11706</v>
       </c>
-      <c r="M82" s="10">
-        <f t="shared" si="98"/>
+      <c r="M88" s="10">
+        <f t="shared" si="113"/>
         <v>11622</v>
       </c>
-      <c r="N82" s="10">
-        <f t="shared" si="98"/>
+      <c r="N88" s="10">
+        <f t="shared" si="113"/>
         <v>12820</v>
       </c>
-      <c r="O82" s="10">
-        <f>SUM(L79:O79)</f>
+      <c r="O88" s="10">
+        <f>SUM(L85:O85)</f>
         <v>12926</v>
       </c>
     </row>
-    <row r="83" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B83" s="1" t="s">
+    <row r="89" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="B89" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="J83" s="10">
-        <f t="shared" ref="J83:N83" si="99">SUM(G80:J80)</f>
+      <c r="J89" s="10">
+        <f t="shared" ref="J89:N89" si="114">SUM(G86:J86)</f>
         <v>10110</v>
       </c>
-      <c r="K83" s="10">
-        <f t="shared" si="99"/>
+      <c r="K89" s="10">
+        <f t="shared" si="114"/>
         <v>10479</v>
       </c>
-      <c r="L83" s="10">
-        <f t="shared" si="99"/>
+      <c r="L89" s="10">
+        <f t="shared" si="114"/>
         <v>11016</v>
       </c>
-      <c r="M83" s="10">
-        <f t="shared" si="99"/>
+      <c r="M89" s="10">
+        <f t="shared" si="114"/>
         <v>11573</v>
       </c>
-      <c r="N83" s="10">
-        <f t="shared" si="99"/>
+      <c r="N89" s="10">
+        <f t="shared" si="114"/>
         <v>5541</v>
       </c>
-      <c r="O83" s="10">
-        <f>SUM(L80:O80)</f>
+      <c r="O89" s="10">
+        <f>SUM(L86:O86)</f>
         <v>5365</v>
       </c>
     </row>
